--- a/Master Data Header Description Final.xlsx
+++ b/Master Data Header Description Final.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MVVNL\July 24\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECTS\Query_builderv3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0226DFD-E7BB-4CB8-9D83-4B6199A77A7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Billing master data" sheetId="1" r:id="rId1"/>
@@ -18,10 +19,19 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Billing master data'!$A$2:$F$346</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Billing master data'!$1:$3</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -6246,7 +6256,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0."/>
   </numFmts>
@@ -6993,7 +7003,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -7007,7 +7017,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7019,22 +7029,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -7052,64 +7059,52 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
@@ -7160,67 +7155,64 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7250,8 +7242,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7261,21 +7256,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7295,63 +7275,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -7366,6 +7289,57 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7680,2615 +7654,2615 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G362"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="10"/>
-    <col min="2" max="2" width="37.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="39.85546875" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="82.140625" style="17" customWidth="1"/>
-    <col min="7" max="7" width="28.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="10"/>
+    <col min="1" max="1" width="9.1796875" style="9"/>
+    <col min="2" max="2" width="37.81640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="57.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.26953125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="39.81640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="82.1796875" style="16" customWidth="1"/>
+    <col min="7" max="7" width="28.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.1796875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="93" t="s">
+    <row r="1" spans="1:7" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="111" t="s">
         <v>811</v>
       </c>
-      <c r="B1" s="93"/>
-      <c r="C1" s="93"/>
-      <c r="D1" s="93"/>
-      <c r="E1" s="93"/>
-      <c r="F1" s="93"/>
-      <c r="G1" s="93"/>
-    </row>
-    <row r="2" spans="1:7" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+    </row>
+    <row r="2" spans="1:7" ht="71.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="D2" s="44" t="s">
+      <c r="D2" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="E2" s="45" t="s">
+      <c r="E2" s="40" t="s">
         <v>535</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="41" t="s">
         <v>335</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="42" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="86">
+    <row r="3" spans="1:7" ht="19" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="80">
         <v>1</v>
       </c>
-      <c r="B3" s="86">
+      <c r="B3" s="80">
         <v>2</v>
       </c>
-      <c r="C3" s="86">
+      <c r="C3" s="80">
         <v>3</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="80">
         <v>4</v>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="80">
         <v>5</v>
       </c>
-      <c r="F3" s="86">
+      <c r="F3" s="80">
         <v>6</v>
       </c>
-      <c r="G3" s="86">
+      <c r="G3" s="80">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="48">
+    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="43">
         <v>1</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="45" t="s">
         <v>284</v>
       </c>
-      <c r="D4" s="50"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="52" t="s">
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="47" t="s">
         <v>801</v>
       </c>
-      <c r="G4" s="53"/>
-    </row>
-    <row r="5" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="54">
+      <c r="G4" s="48"/>
+    </row>
+    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="49">
         <v>2</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>285</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="18" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="G5" s="55"/>
-    </row>
-    <row r="6" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="54">
+      <c r="G5" s="50"/>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="49">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>286</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="18" t="s">
+      <c r="E6" s="25"/>
+      <c r="F6" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="G6" s="55"/>
-    </row>
-    <row r="7" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="54">
+      <c r="G6" s="50"/>
+    </row>
+    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="49">
         <v>4</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>130</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="30"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="G7" s="55"/>
-    </row>
-    <row r="8" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="54">
+      <c r="G7" s="50"/>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="49">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>131</v>
       </c>
       <c r="D8" s="4"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="18" t="s">
+      <c r="E8" s="25"/>
+      <c r="F8" s="17" t="s">
         <v>805</v>
       </c>
-      <c r="G8" s="55"/>
-    </row>
-    <row r="9" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="54">
+      <c r="G8" s="50"/>
+    </row>
+    <row r="9" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="49">
         <v>6</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>131</v>
       </c>
       <c r="D9" s="4"/>
-      <c r="E9" s="30"/>
-      <c r="F9" s="18" t="s">
+      <c r="E9" s="25"/>
+      <c r="F9" s="17" t="s">
         <v>805</v>
       </c>
-      <c r="G9" s="55"/>
-    </row>
-    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="54">
+      <c r="G9" s="50"/>
+    </row>
+    <row r="10" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="49">
         <v>7</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D10" s="4"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="18" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="17" t="s">
         <v>806</v>
       </c>
-      <c r="G10" s="55"/>
-    </row>
-    <row r="11" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="54">
+      <c r="G10" s="50"/>
+    </row>
+    <row r="11" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="49">
         <v>8</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>133</v>
       </c>
       <c r="D11" s="4"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="18" t="s">
+      <c r="E11" s="25"/>
+      <c r="F11" s="17" t="s">
         <v>807</v>
       </c>
-      <c r="G11" s="55"/>
-    </row>
-    <row r="12" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="54">
+      <c r="G11" s="50"/>
+    </row>
+    <row r="12" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="49">
         <v>9</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>134</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="18" t="s">
+      <c r="E12" s="25"/>
+      <c r="F12" s="17" t="s">
         <v>808</v>
       </c>
-      <c r="G12" s="55"/>
-    </row>
-    <row r="13" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="54">
+      <c r="G12" s="50"/>
+    </row>
+    <row r="13" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="49">
         <v>10</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>135</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="30"/>
-      <c r="F13" s="18" t="s">
+      <c r="E13" s="25"/>
+      <c r="F13" s="17" t="s">
         <v>809</v>
       </c>
-      <c r="G13" s="55"/>
-    </row>
-    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="87">
+      <c r="G13" s="50"/>
+    </row>
+    <row r="14" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A14" s="82">
         <v>11</v>
       </c>
-      <c r="B14" s="98" t="s">
+      <c r="B14" s="88" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="104" t="s">
+      <c r="C14" s="96" t="s">
         <v>287</v>
       </c>
-      <c r="D14" s="104" t="s">
+      <c r="D14" s="96" t="s">
         <v>419</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="10" t="s">
         <v>420</v>
       </c>
-      <c r="F14" s="23" t="s">
+      <c r="F14" s="21" t="s">
         <v>422</v>
       </c>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="51" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="88"/>
-      <c r="B15" s="99"/>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="11" t="s">
+    <row r="15" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A15" s="83"/>
+      <c r="B15" s="89"/>
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="10" t="s">
         <v>421</v>
       </c>
-      <c r="F15" s="23" t="s">
+      <c r="F15" s="21" t="s">
         <v>423</v>
       </c>
-      <c r="G15" s="56" t="s">
+      <c r="G15" s="51" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="88"/>
-      <c r="B16" s="99"/>
-      <c r="C16" s="105"/>
-      <c r="D16" s="105"/>
-      <c r="E16" s="31">
+    <row r="16" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A16" s="83"/>
+      <c r="B16" s="89"/>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="26">
         <v>11</v>
       </c>
-      <c r="F16" s="23" t="s">
+      <c r="F16" s="21" t="s">
         <v>424</v>
       </c>
-      <c r="G16" s="57" t="s">
+      <c r="G16" s="52" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A17" s="88"/>
-      <c r="B17" s="99"/>
-      <c r="C17" s="105"/>
-      <c r="D17" s="105"/>
-      <c r="E17" s="31">
+    <row r="17" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A17" s="83"/>
+      <c r="B17" s="89"/>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="26">
         <v>12</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="G17" s="57" t="s">
+      <c r="G17" s="52" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="88"/>
-      <c r="B18" s="99"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="105"/>
-      <c r="E18" s="31">
+    <row r="18" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A18" s="83"/>
+      <c r="B18" s="89"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="26">
         <v>13</v>
       </c>
-      <c r="F18" s="24" t="s">
+      <c r="F18" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="G18" s="57" t="s">
+      <c r="G18" s="52" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
-      <c r="B19" s="99"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="105"/>
-      <c r="E19" s="31">
+    <row r="19" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="83"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="26">
         <v>14</v>
       </c>
-      <c r="F19" s="23" t="s">
+      <c r="F19" s="21" t="s">
         <v>427</v>
       </c>
-      <c r="G19" s="58" t="s">
+      <c r="G19" s="53" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="88"/>
-      <c r="B20" s="99"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="31">
+    <row r="20" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="83"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="26">
         <v>15</v>
       </c>
-      <c r="F20" s="23" t="s">
+      <c r="F20" s="21" t="s">
         <v>428</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="54" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="88"/>
-      <c r="B21" s="99"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="31">
+    <row r="21" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A21" s="83"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="26">
         <v>17</v>
       </c>
-      <c r="F21" s="23" t="s">
+      <c r="F21" s="21" t="s">
         <v>429</v>
       </c>
-      <c r="G21" s="57" t="s">
+      <c r="G21" s="52" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="88"/>
-      <c r="B22" s="99"/>
-      <c r="C22" s="105"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="31">
+    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A22" s="83"/>
+      <c r="B22" s="89"/>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="26">
         <v>18</v>
       </c>
-      <c r="F22" s="23" t="s">
+      <c r="F22" s="21" t="s">
         <v>430</v>
       </c>
-      <c r="G22" s="57" t="s">
+      <c r="G22" s="52" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="88"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="105"/>
-      <c r="D23" s="105"/>
-      <c r="E23" s="31">
+    <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A23" s="83"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="99"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="26">
         <v>19</v>
       </c>
-      <c r="F23" s="23" t="s">
+      <c r="F23" s="21" t="s">
         <v>431</v>
       </c>
-      <c r="G23" s="57" t="s">
+      <c r="G23" s="52" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="88"/>
-      <c r="B24" s="99"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="101" t="s">
+    <row r="24" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A24" s="83"/>
+      <c r="B24" s="89"/>
+      <c r="C24" s="99"/>
+      <c r="D24" s="100" t="s">
         <v>435</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="26">
         <v>20</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F24" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="G24" s="56" t="s">
+      <c r="G24" s="51" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="88"/>
-      <c r="B25" s="99"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="31">
+    <row r="25" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A25" s="83"/>
+      <c r="B25" s="89"/>
+      <c r="C25" s="99"/>
+      <c r="D25" s="101"/>
+      <c r="E25" s="26">
         <v>22</v>
       </c>
-      <c r="F25" s="23" t="s">
+      <c r="F25" s="21" t="s">
         <v>437</v>
       </c>
-      <c r="G25" s="57" t="s">
+      <c r="G25" s="52" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="88"/>
-      <c r="B26" s="99"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="102"/>
-      <c r="E26" s="31">
+    <row r="26" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A26" s="83"/>
+      <c r="B26" s="89"/>
+      <c r="C26" s="99"/>
+      <c r="D26" s="101"/>
+      <c r="E26" s="26">
         <v>23</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="21" t="s">
         <v>438</v>
       </c>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="52" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="88"/>
-      <c r="B27" s="99"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="102"/>
-      <c r="E27" s="31">
+    <row r="27" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A27" s="83"/>
+      <c r="B27" s="89"/>
+      <c r="C27" s="99"/>
+      <c r="D27" s="101"/>
+      <c r="E27" s="26">
         <v>24</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="21" t="s">
         <v>439</v>
       </c>
-      <c r="G27" s="57" t="s">
+      <c r="G27" s="52" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="88"/>
-      <c r="B28" s="99"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="102"/>
-      <c r="E28" s="11" t="s">
+    <row r="28" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A28" s="83"/>
+      <c r="B28" s="89"/>
+      <c r="C28" s="99"/>
+      <c r="D28" s="101"/>
+      <c r="E28" s="10" t="s">
         <v>432</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="21" t="s">
         <v>440</v>
       </c>
-      <c r="G28" s="60" t="s">
+      <c r="G28" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="88"/>
-      <c r="B29" s="99"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="102"/>
-      <c r="E29" s="11" t="s">
+    <row r="29" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A29" s="83"/>
+      <c r="B29" s="89"/>
+      <c r="C29" s="99"/>
+      <c r="D29" s="101"/>
+      <c r="E29" s="10" t="s">
         <v>433</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="21" t="s">
         <v>441</v>
       </c>
-      <c r="G29" s="60" t="s">
+      <c r="G29" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="88"/>
-      <c r="B30" s="99"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="102"/>
-      <c r="E30" s="11" t="s">
+    <row r="30" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A30" s="83"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="99"/>
+      <c r="D30" s="101"/>
+      <c r="E30" s="10" t="s">
         <v>434</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="21" t="s">
         <v>442</v>
       </c>
-      <c r="G30" s="60" t="s">
+      <c r="G30" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="88"/>
-      <c r="B31" s="99"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="31">
+    <row r="31" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A31" s="83"/>
+      <c r="B31" s="89"/>
+      <c r="C31" s="99"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="26">
         <v>25</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="21" t="s">
         <v>443</v>
       </c>
-      <c r="G31" s="60" t="s">
+      <c r="G31" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="88"/>
-      <c r="B32" s="99"/>
-      <c r="C32" s="105"/>
-      <c r="D32" s="102"/>
-      <c r="E32" s="31">
+    <row r="32" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A32" s="83"/>
+      <c r="B32" s="89"/>
+      <c r="C32" s="99"/>
+      <c r="D32" s="101"/>
+      <c r="E32" s="26">
         <v>26</v>
       </c>
-      <c r="F32" s="25" t="s">
+      <c r="F32" s="22" t="s">
         <v>641</v>
       </c>
-      <c r="G32" s="60" t="s">
+      <c r="G32" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="88"/>
-      <c r="B33" s="99"/>
-      <c r="C33" s="105"/>
-      <c r="D33" s="102"/>
-      <c r="E33" s="31">
+    <row r="33" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A33" s="83"/>
+      <c r="B33" s="89"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="101"/>
+      <c r="E33" s="26">
         <v>27</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="G33" s="61" t="s">
+      <c r="G33" s="56" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="88"/>
-      <c r="B34" s="99"/>
-      <c r="C34" s="105"/>
-      <c r="D34" s="103"/>
-      <c r="E34" s="31">
+    <row r="34" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A34" s="83"/>
+      <c r="B34" s="89"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="102"/>
+      <c r="E34" s="26">
         <v>28</v>
       </c>
-      <c r="F34" s="23" t="s">
+      <c r="F34" s="21" t="s">
         <v>445</v>
       </c>
-      <c r="G34" s="60" t="s">
+      <c r="G34" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="88"/>
-      <c r="B35" s="99"/>
-      <c r="C35" s="105"/>
-      <c r="D35" s="101" t="s">
+    <row r="35" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A35" s="83"/>
+      <c r="B35" s="89"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="100" t="s">
         <v>460</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="26">
         <v>30</v>
       </c>
-      <c r="F35" s="23" t="s">
+      <c r="F35" s="21" t="s">
         <v>452</v>
       </c>
-      <c r="G35" s="60" t="s">
+      <c r="G35" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="88"/>
-      <c r="B36" s="99"/>
-      <c r="C36" s="105"/>
-      <c r="D36" s="102"/>
-      <c r="E36" s="31">
+    <row r="36" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A36" s="83"/>
+      <c r="B36" s="89"/>
+      <c r="C36" s="99"/>
+      <c r="D36" s="101"/>
+      <c r="E36" s="26">
         <v>31</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="57" t="s">
         <v>462</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="88"/>
-      <c r="B37" s="99"/>
-      <c r="C37" s="105"/>
-      <c r="D37" s="102"/>
-      <c r="E37" s="31">
+    <row r="37" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A37" s="83"/>
+      <c r="B37" s="89"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="26">
         <v>32</v>
       </c>
-      <c r="F37" s="23" t="s">
+      <c r="F37" s="21" t="s">
         <v>453</v>
       </c>
-      <c r="G37" s="60" t="s">
+      <c r="G37" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="88"/>
-      <c r="B38" s="99"/>
-      <c r="C38" s="105"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="31">
+    <row r="38" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A38" s="83"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="99"/>
+      <c r="D38" s="101"/>
+      <c r="E38" s="26">
         <v>33</v>
       </c>
-      <c r="F38" s="23" t="s">
+      <c r="F38" s="21" t="s">
         <v>454</v>
       </c>
-      <c r="G38" s="60" t="s">
+      <c r="G38" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A39" s="88"/>
-      <c r="B39" s="99"/>
-      <c r="C39" s="105"/>
-      <c r="D39" s="102"/>
-      <c r="E39" s="31">
+    <row r="39" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A39" s="83"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="99"/>
+      <c r="D39" s="101"/>
+      <c r="E39" s="26">
         <v>34</v>
       </c>
-      <c r="F39" s="23" t="s">
+      <c r="F39" s="21" t="s">
         <v>455</v>
       </c>
-      <c r="G39" s="61" t="s">
+      <c r="G39" s="56" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A40" s="88"/>
-      <c r="B40" s="99"/>
-      <c r="C40" s="105"/>
-      <c r="D40" s="102"/>
-      <c r="E40" s="31">
+    <row r="40" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="83"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="99"/>
+      <c r="D40" s="101"/>
+      <c r="E40" s="26">
         <v>35</v>
       </c>
-      <c r="F40" s="23" t="s">
+      <c r="F40" s="21" t="s">
         <v>456</v>
       </c>
-      <c r="G40" s="63" t="s">
+      <c r="G40" s="58" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="88"/>
-      <c r="B41" s="99"/>
-      <c r="C41" s="105"/>
-      <c r="D41" s="102"/>
-      <c r="E41" s="31">
+    <row r="41" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A41" s="83"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="99"/>
+      <c r="D41" s="101"/>
+      <c r="E41" s="26">
         <v>36</v>
       </c>
-      <c r="F41" s="23" t="s">
+      <c r="F41" s="21" t="s">
         <v>457</v>
       </c>
-      <c r="G41" s="60" t="s">
+      <c r="G41" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A42" s="88"/>
-      <c r="B42" s="99"/>
-      <c r="C42" s="105"/>
-      <c r="D42" s="102"/>
-      <c r="E42" s="31">
+    <row r="42" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A42" s="83"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="99"/>
+      <c r="D42" s="101"/>
+      <c r="E42" s="26">
         <v>37</v>
       </c>
-      <c r="F42" s="24" t="s">
+      <c r="F42" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="G42" s="60" t="s">
+      <c r="G42" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="88"/>
-      <c r="B43" s="99"/>
-      <c r="C43" s="105"/>
-      <c r="D43" s="103"/>
-      <c r="E43" s="31">
+    <row r="43" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A43" s="83"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="26">
         <v>38</v>
       </c>
-      <c r="F43" s="24" t="s">
+      <c r="F43" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="G43" s="60" t="s">
+      <c r="G43" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="88"/>
-      <c r="B44" s="99"/>
-      <c r="C44" s="105"/>
-      <c r="D44" s="101" t="s">
+    <row r="44" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A44" s="83"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="100" t="s">
         <v>467</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="27">
         <v>40</v>
       </c>
-      <c r="F44" s="23" t="s">
+      <c r="F44" s="21" t="s">
         <v>468</v>
       </c>
-      <c r="G44" s="60" t="s">
+      <c r="G44" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A45" s="88"/>
-      <c r="B45" s="99"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="102"/>
-      <c r="E45" s="33" t="s">
+    <row r="45" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A45" s="83"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="28" t="s">
         <v>464</v>
       </c>
-      <c r="F45" s="24" t="s">
+      <c r="F45" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="59" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="88"/>
-      <c r="B46" s="99"/>
-      <c r="C46" s="105"/>
-      <c r="D46" s="102"/>
-      <c r="E46" s="31">
+    <row r="46" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A46" s="83"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="99"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="26">
         <v>41</v>
       </c>
-      <c r="F46" s="24" t="s">
+      <c r="F46" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="G46" s="65" t="s">
+      <c r="G46" s="60" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="88"/>
-      <c r="B47" s="99"/>
-      <c r="C47" s="105"/>
-      <c r="D47" s="102"/>
-      <c r="E47" s="11" t="s">
+    <row r="47" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A47" s="83"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="99"/>
+      <c r="D47" s="101"/>
+      <c r="E47" s="10" t="s">
         <v>465</v>
       </c>
-      <c r="F47" s="23" t="s">
+      <c r="F47" s="21" t="s">
         <v>471</v>
       </c>
-      <c r="G47" s="60" t="s">
+      <c r="G47" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="35.25" x14ac:dyDescent="0.25">
-      <c r="A48" s="88"/>
-      <c r="B48" s="99"/>
-      <c r="C48" s="105"/>
-      <c r="D48" s="102"/>
-      <c r="E48" s="31">
+    <row r="48" spans="1:7" ht="35" x14ac:dyDescent="0.35">
+      <c r="A48" s="83"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="99"/>
+      <c r="D48" s="101"/>
+      <c r="E48" s="26">
         <v>42</v>
       </c>
-      <c r="F48" s="24" t="s">
+      <c r="F48" s="6" t="s">
         <v>472</v>
       </c>
-      <c r="G48" s="66" t="s">
+      <c r="G48" s="61" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="88"/>
-      <c r="B49" s="99"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="102"/>
-      <c r="E49" s="11" t="s">
+    <row r="49" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A49" s="83"/>
+      <c r="B49" s="89"/>
+      <c r="C49" s="99"/>
+      <c r="D49" s="101"/>
+      <c r="E49" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="F49" s="23" t="s">
+      <c r="F49" s="21" t="s">
         <v>473</v>
       </c>
-      <c r="G49" s="60" t="s">
+      <c r="G49" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="88"/>
-      <c r="B50" s="99"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="34">
+    <row r="50" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A50" s="83"/>
+      <c r="B50" s="89"/>
+      <c r="C50" s="99"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="29">
         <v>43</v>
       </c>
-      <c r="F50" s="23" t="s">
+      <c r="F50" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="G50" s="60" t="s">
+      <c r="G50" s="55" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="88"/>
-      <c r="B51" s="99"/>
-      <c r="C51" s="105"/>
-      <c r="D51" s="102"/>
-      <c r="E51" s="35">
+    <row r="51" spans="1:7" ht="45" x14ac:dyDescent="0.35">
+      <c r="A51" s="83"/>
+      <c r="B51" s="89"/>
+      <c r="C51" s="99"/>
+      <c r="D51" s="101"/>
+      <c r="E51" s="30">
         <v>44</v>
       </c>
-      <c r="F51" s="24" t="s">
+      <c r="F51" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="G51" s="67" t="s">
+      <c r="G51" s="62" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="39" x14ac:dyDescent="0.25">
-      <c r="A52" s="88"/>
-      <c r="B52" s="99"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="31">
+    <row r="52" spans="1:7" ht="34" x14ac:dyDescent="0.35">
+      <c r="A52" s="83"/>
+      <c r="B52" s="89"/>
+      <c r="C52" s="99"/>
+      <c r="D52" s="101"/>
+      <c r="E52" s="26">
         <v>46</v>
       </c>
-      <c r="F52" s="26" t="s">
+      <c r="F52" s="23" t="s">
         <v>481</v>
       </c>
-      <c r="G52" s="68" t="s">
+      <c r="G52" s="63" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="88"/>
-      <c r="B53" s="99"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="103"/>
-      <c r="E53" s="31">
+    <row r="53" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A53" s="83"/>
+      <c r="B53" s="89"/>
+      <c r="C53" s="99"/>
+      <c r="D53" s="102"/>
+      <c r="E53" s="26">
         <v>47</v>
       </c>
-      <c r="F53" s="27" t="s">
+      <c r="F53" s="24" t="s">
         <v>482</v>
       </c>
-      <c r="G53" s="60" t="s">
+      <c r="G53" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="88"/>
-      <c r="B54" s="99"/>
-      <c r="C54" s="105"/>
-      <c r="D54" s="101" t="s">
+    <row r="54" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A54" s="83"/>
+      <c r="B54" s="89"/>
+      <c r="C54" s="99"/>
+      <c r="D54" s="100" t="s">
         <v>483</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="26">
         <v>50</v>
       </c>
-      <c r="F54" s="23" t="s">
+      <c r="F54" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="G54" s="60" t="s">
+      <c r="G54" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="88"/>
-      <c r="B55" s="99"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="102"/>
-      <c r="E55" s="31">
+    <row r="55" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A55" s="83"/>
+      <c r="B55" s="89"/>
+      <c r="C55" s="99"/>
+      <c r="D55" s="101"/>
+      <c r="E55" s="26">
         <v>51</v>
       </c>
-      <c r="F55" s="23" t="s">
+      <c r="F55" s="21" t="s">
         <v>486</v>
       </c>
-      <c r="G55" s="60" t="s">
+      <c r="G55" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="88"/>
-      <c r="B56" s="99"/>
-      <c r="C56" s="105"/>
-      <c r="D56" s="102"/>
-      <c r="E56" s="31">
+    <row r="56" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="83"/>
+      <c r="B56" s="89"/>
+      <c r="C56" s="99"/>
+      <c r="D56" s="101"/>
+      <c r="E56" s="26">
         <v>52</v>
       </c>
-      <c r="F56" s="23" t="s">
+      <c r="F56" s="21" t="s">
         <v>487</v>
       </c>
-      <c r="G56" s="68" t="s">
+      <c r="G56" s="63" t="s">
         <v>480</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A57" s="88"/>
-      <c r="B57" s="99"/>
-      <c r="C57" s="105"/>
-      <c r="D57" s="102"/>
-      <c r="E57" s="31">
+    <row r="57" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A57" s="83"/>
+      <c r="B57" s="89"/>
+      <c r="C57" s="99"/>
+      <c r="D57" s="101"/>
+      <c r="E57" s="26">
         <v>53</v>
       </c>
-      <c r="F57" s="23" t="s">
+      <c r="F57" s="21" t="s">
         <v>488</v>
       </c>
-      <c r="G57" s="60" t="s">
+      <c r="G57" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A58" s="88"/>
-      <c r="B58" s="99"/>
-      <c r="C58" s="105"/>
-      <c r="D58" s="102"/>
-      <c r="E58" s="33">
+    <row r="58" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A58" s="83"/>
+      <c r="B58" s="89"/>
+      <c r="C58" s="99"/>
+      <c r="D58" s="101"/>
+      <c r="E58" s="28">
         <v>54</v>
       </c>
-      <c r="F58" s="23" t="s">
+      <c r="F58" s="21" t="s">
         <v>489</v>
       </c>
-      <c r="G58" s="60" t="s">
+      <c r="G58" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A59" s="88"/>
-      <c r="B59" s="99"/>
-      <c r="C59" s="105"/>
-      <c r="D59" s="102"/>
-      <c r="E59" s="31">
+    <row r="59" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A59" s="83"/>
+      <c r="B59" s="89"/>
+      <c r="C59" s="99"/>
+      <c r="D59" s="101"/>
+      <c r="E59" s="26">
         <v>55</v>
       </c>
-      <c r="F59" s="23" t="s">
+      <c r="F59" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="G59" s="60" t="s">
+      <c r="G59" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="88"/>
-      <c r="B60" s="99"/>
-      <c r="C60" s="105"/>
-      <c r="D60" s="102"/>
-      <c r="E60" s="31">
+    <row r="60" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A60" s="83"/>
+      <c r="B60" s="89"/>
+      <c r="C60" s="99"/>
+      <c r="D60" s="101"/>
+      <c r="E60" s="26">
         <v>56</v>
       </c>
-      <c r="F60" s="23" t="s">
+      <c r="F60" s="21" t="s">
         <v>491</v>
       </c>
-      <c r="G60" s="60" t="s">
+      <c r="G60" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A61" s="88"/>
-      <c r="B61" s="99"/>
-      <c r="C61" s="105"/>
-      <c r="D61" s="102"/>
-      <c r="E61" s="31">
+    <row r="61" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A61" s="83"/>
+      <c r="B61" s="89"/>
+      <c r="C61" s="99"/>
+      <c r="D61" s="101"/>
+      <c r="E61" s="26">
         <v>57</v>
       </c>
-      <c r="F61" s="23" t="s">
+      <c r="F61" s="21" t="s">
         <v>492</v>
       </c>
-      <c r="G61" s="60" t="s">
+      <c r="G61" s="55" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="88"/>
-      <c r="B62" s="99"/>
-      <c r="C62" s="105"/>
-      <c r="D62" s="102"/>
-      <c r="E62" s="12" t="s">
+    <row r="62" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A62" s="83"/>
+      <c r="B62" s="89"/>
+      <c r="C62" s="99"/>
+      <c r="D62" s="101"/>
+      <c r="E62" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="F62" s="24" t="s">
+      <c r="F62" s="6" t="s">
         <v>493</v>
       </c>
-      <c r="G62" s="65" t="s">
+      <c r="G62" s="60" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A63" s="88"/>
-      <c r="B63" s="99"/>
-      <c r="C63" s="105"/>
-      <c r="D63" s="103"/>
-      <c r="E63" s="31">
+    <row r="63" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A63" s="83"/>
+      <c r="B63" s="89"/>
+      <c r="C63" s="99"/>
+      <c r="D63" s="102"/>
+      <c r="E63" s="26">
         <v>58</v>
       </c>
-      <c r="F63" s="24" t="s">
+      <c r="F63" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="G63" s="69" t="s">
+      <c r="G63" s="64" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A64" s="88"/>
-      <c r="B64" s="99"/>
-      <c r="C64" s="105"/>
-      <c r="D64" s="101" t="s">
+    <row r="64" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A64" s="83"/>
+      <c r="B64" s="89"/>
+      <c r="C64" s="99"/>
+      <c r="D64" s="100" t="s">
         <v>497</v>
       </c>
-      <c r="E64" s="31">
+      <c r="E64" s="26">
         <v>60</v>
       </c>
-      <c r="F64" s="23" t="s">
+      <c r="F64" s="21" t="s">
         <v>509</v>
       </c>
-      <c r="G64" s="60" t="s">
+      <c r="G64" s="55" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A65" s="88"/>
-      <c r="B65" s="99"/>
-      <c r="C65" s="105"/>
-      <c r="D65" s="102"/>
-      <c r="E65" s="31">
+    <row r="65" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A65" s="83"/>
+      <c r="B65" s="89"/>
+      <c r="C65" s="99"/>
+      <c r="D65" s="101"/>
+      <c r="E65" s="26">
         <v>61</v>
       </c>
-      <c r="F65" s="23" t="s">
+      <c r="F65" s="21" t="s">
         <v>498</v>
       </c>
-      <c r="G65" s="60" t="s">
+      <c r="G65" s="55" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="88"/>
-      <c r="B66" s="99"/>
-      <c r="C66" s="105"/>
-      <c r="D66" s="102"/>
-      <c r="E66" s="31">
+    <row r="66" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A66" s="83"/>
+      <c r="B66" s="89"/>
+      <c r="C66" s="99"/>
+      <c r="D66" s="101"/>
+      <c r="E66" s="26">
         <v>62</v>
       </c>
-      <c r="F66" s="23" t="s">
+      <c r="F66" s="21" t="s">
         <v>499</v>
       </c>
-      <c r="G66" s="60" t="s">
+      <c r="G66" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A67" s="88"/>
-      <c r="B67" s="99"/>
-      <c r="C67" s="105"/>
-      <c r="D67" s="102"/>
-      <c r="E67" s="11" t="s">
+    <row r="67" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A67" s="83"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="99"/>
+      <c r="D67" s="101"/>
+      <c r="E67" s="10" t="s">
         <v>496</v>
       </c>
-      <c r="F67" s="23" t="s">
+      <c r="F67" s="21" t="s">
         <v>500</v>
       </c>
-      <c r="G67" s="60" t="s">
+      <c r="G67" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A68" s="88"/>
-      <c r="B68" s="99"/>
-      <c r="C68" s="105"/>
-      <c r="D68" s="102"/>
-      <c r="E68" s="31">
+    <row r="68" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A68" s="83"/>
+      <c r="B68" s="89"/>
+      <c r="C68" s="99"/>
+      <c r="D68" s="101"/>
+      <c r="E68" s="26">
         <v>63</v>
       </c>
-      <c r="F68" s="24" t="s">
+      <c r="F68" s="6" t="s">
         <v>502</v>
       </c>
-      <c r="G68" s="60" t="s">
+      <c r="G68" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A69" s="88"/>
-      <c r="B69" s="99"/>
-      <c r="C69" s="105"/>
-      <c r="D69" s="102"/>
-      <c r="E69" s="31">
+    <row r="69" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A69" s="83"/>
+      <c r="B69" s="89"/>
+      <c r="C69" s="99"/>
+      <c r="D69" s="101"/>
+      <c r="E69" s="26">
         <v>64</v>
       </c>
-      <c r="F69" s="23" t="s">
+      <c r="F69" s="21" t="s">
         <v>503</v>
       </c>
-      <c r="G69" s="60" t="s">
+      <c r="G69" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="88"/>
-      <c r="B70" s="99"/>
-      <c r="C70" s="105"/>
-      <c r="D70" s="102"/>
-      <c r="E70" s="31">
+    <row r="70" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A70" s="83"/>
+      <c r="B70" s="89"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="101"/>
+      <c r="E70" s="26">
         <v>65</v>
       </c>
-      <c r="F70" s="23" t="s">
+      <c r="F70" s="21" t="s">
         <v>504</v>
       </c>
-      <c r="G70" s="60" t="s">
+      <c r="G70" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="32.25" x14ac:dyDescent="0.25">
-      <c r="A71" s="88"/>
-      <c r="B71" s="99"/>
-      <c r="C71" s="105"/>
-      <c r="D71" s="102"/>
-      <c r="E71" s="31">
+    <row r="71" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
+      <c r="A71" s="83"/>
+      <c r="B71" s="89"/>
+      <c r="C71" s="99"/>
+      <c r="D71" s="101"/>
+      <c r="E71" s="26">
         <v>66</v>
       </c>
-      <c r="F71" s="24" t="s">
+      <c r="F71" s="6" t="s">
         <v>505</v>
       </c>
-      <c r="G71" s="60" t="s">
+      <c r="G71" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="88"/>
-      <c r="B72" s="99"/>
-      <c r="C72" s="105"/>
-      <c r="D72" s="102"/>
-      <c r="E72" s="36">
+    <row r="72" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A72" s="83"/>
+      <c r="B72" s="89"/>
+      <c r="C72" s="99"/>
+      <c r="D72" s="101"/>
+      <c r="E72" s="31">
         <v>67</v>
       </c>
-      <c r="F72" s="23" t="s">
+      <c r="F72" s="21" t="s">
         <v>506</v>
       </c>
-      <c r="G72" s="60" t="s">
+      <c r="G72" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A73" s="88"/>
-      <c r="B73" s="99"/>
-      <c r="C73" s="105"/>
-      <c r="D73" s="103"/>
-      <c r="E73" s="31">
+    <row r="73" spans="1:7" ht="32" x14ac:dyDescent="0.35">
+      <c r="A73" s="83"/>
+      <c r="B73" s="89"/>
+      <c r="C73" s="99"/>
+      <c r="D73" s="102"/>
+      <c r="E73" s="26">
         <v>68</v>
       </c>
-      <c r="F73" s="23" t="s">
+      <c r="F73" s="21" t="s">
         <v>507</v>
       </c>
-      <c r="G73" s="60" t="s">
+      <c r="G73" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="33" x14ac:dyDescent="0.25">
-      <c r="A74" s="88"/>
-      <c r="B74" s="99"/>
-      <c r="C74" s="105"/>
-      <c r="D74" s="107" t="s">
+    <row r="74" spans="1:7" ht="32.5" x14ac:dyDescent="0.35">
+      <c r="A74" s="83"/>
+      <c r="B74" s="89"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="105" t="s">
         <v>534</v>
       </c>
-      <c r="E74" s="11" t="s">
+      <c r="E74" s="10" t="s">
         <v>510</v>
       </c>
-      <c r="F74" s="24" t="s">
+      <c r="F74" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="G74" s="70" t="s">
+      <c r="G74" s="65" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="18" x14ac:dyDescent="0.25">
-      <c r="A75" s="88"/>
-      <c r="B75" s="99"/>
-      <c r="C75" s="105"/>
-      <c r="D75" s="108"/>
-      <c r="E75" s="11" t="s">
+    <row r="75" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A75" s="83"/>
+      <c r="B75" s="89"/>
+      <c r="C75" s="99"/>
+      <c r="D75" s="106"/>
+      <c r="E75" s="10" t="s">
         <v>511</v>
       </c>
-      <c r="F75" s="23" t="s">
+      <c r="F75" s="21" t="s">
         <v>514</v>
       </c>
-      <c r="G75" s="71" t="s">
+      <c r="G75" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="88"/>
-      <c r="B76" s="99"/>
-      <c r="C76" s="105"/>
-      <c r="D76" s="108"/>
-      <c r="E76" s="30">
+    <row r="76" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A76" s="83"/>
+      <c r="B76" s="89"/>
+      <c r="C76" s="99"/>
+      <c r="D76" s="106"/>
+      <c r="E76" s="25">
         <v>72</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F76" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="G76" s="71" t="s">
+      <c r="G76" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A77" s="88"/>
-      <c r="B77" s="99"/>
-      <c r="C77" s="105"/>
-      <c r="D77" s="108"/>
-      <c r="E77" s="30">
+    <row r="77" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A77" s="83"/>
+      <c r="B77" s="89"/>
+      <c r="C77" s="99"/>
+      <c r="D77" s="106"/>
+      <c r="E77" s="25">
         <v>73</v>
       </c>
-      <c r="F77" s="13" t="s">
+      <c r="F77" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="G77" s="71" t="s">
+      <c r="G77" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A78" s="88"/>
-      <c r="B78" s="99"/>
-      <c r="C78" s="105"/>
-      <c r="D78" s="108"/>
-      <c r="E78" s="30">
+    <row r="78" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A78" s="83"/>
+      <c r="B78" s="89"/>
+      <c r="C78" s="99"/>
+      <c r="D78" s="106"/>
+      <c r="E78" s="25">
         <v>74</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>525</v>
       </c>
-      <c r="G78" s="60" t="s">
+      <c r="G78" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="88"/>
-      <c r="B79" s="99"/>
-      <c r="C79" s="105"/>
-      <c r="D79" s="108"/>
-      <c r="E79" s="30">
+    <row r="79" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A79" s="83"/>
+      <c r="B79" s="89"/>
+      <c r="C79" s="99"/>
+      <c r="D79" s="106"/>
+      <c r="E79" s="25">
         <v>75</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>526</v>
       </c>
-      <c r="G79" s="60" t="s">
+      <c r="G79" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A80" s="88"/>
-      <c r="B80" s="99"/>
-      <c r="C80" s="105"/>
-      <c r="D80" s="108"/>
-      <c r="E80" s="30" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" s="83"/>
+      <c r="B80" s="89"/>
+      <c r="C80" s="99"/>
+      <c r="D80" s="106"/>
+      <c r="E80" s="25" t="s">
         <v>517</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>527</v>
       </c>
-      <c r="G80" s="71" t="s">
+      <c r="G80" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A81" s="88"/>
-      <c r="B81" s="99"/>
-      <c r="C81" s="105"/>
-      <c r="D81" s="108"/>
-      <c r="E81" s="30" t="s">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="83"/>
+      <c r="B81" s="89"/>
+      <c r="C81" s="99"/>
+      <c r="D81" s="106"/>
+      <c r="E81" s="25" t="s">
         <v>518</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>528</v>
       </c>
-      <c r="G81" s="71" t="s">
+      <c r="G81" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A82" s="88"/>
-      <c r="B82" s="99"/>
-      <c r="C82" s="105"/>
-      <c r="D82" s="108"/>
-      <c r="E82" s="30" t="s">
+    <row r="82" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A82" s="83"/>
+      <c r="B82" s="89"/>
+      <c r="C82" s="99"/>
+      <c r="D82" s="106"/>
+      <c r="E82" s="25" t="s">
         <v>519</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>529</v>
       </c>
-      <c r="G82" s="60" t="s">
+      <c r="G82" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A83" s="88"/>
-      <c r="B83" s="99"/>
-      <c r="C83" s="105"/>
-      <c r="D83" s="108"/>
-      <c r="E83" s="30" t="s">
+    <row r="83" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A83" s="83"/>
+      <c r="B83" s="89"/>
+      <c r="C83" s="99"/>
+      <c r="D83" s="106"/>
+      <c r="E83" s="25" t="s">
         <v>520</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="G83" s="60" t="s">
+      <c r="G83" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A84" s="88"/>
-      <c r="B84" s="99"/>
-      <c r="C84" s="105"/>
-      <c r="D84" s="108"/>
-      <c r="E84" s="30" t="s">
+    <row r="84" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A84" s="83"/>
+      <c r="B84" s="89"/>
+      <c r="C84" s="99"/>
+      <c r="D84" s="106"/>
+      <c r="E84" s="25" t="s">
         <v>521</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="G84" s="71" t="s">
+      <c r="G84" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A85" s="88"/>
-      <c r="B85" s="99"/>
-      <c r="C85" s="105"/>
-      <c r="D85" s="108"/>
-      <c r="E85" s="30" t="s">
+    <row r="85" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A85" s="83"/>
+      <c r="B85" s="89"/>
+      <c r="C85" s="99"/>
+      <c r="D85" s="106"/>
+      <c r="E85" s="25" t="s">
         <v>522</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="G85" s="71" t="s">
+      <c r="G85" s="66" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A86" s="88"/>
-      <c r="B86" s="99"/>
-      <c r="C86" s="105"/>
-      <c r="D86" s="108"/>
-      <c r="E86" s="30" t="s">
+    <row r="86" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A86" s="83"/>
+      <c r="B86" s="89"/>
+      <c r="C86" s="99"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="25" t="s">
         <v>523</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="G86" s="60" t="s">
+      <c r="G86" s="55" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="88"/>
-      <c r="B87" s="99"/>
-      <c r="C87" s="105"/>
-      <c r="D87" s="109"/>
-      <c r="E87" s="30" t="s">
+    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A87" s="83"/>
+      <c r="B87" s="89"/>
+      <c r="C87" s="99"/>
+      <c r="D87" s="107"/>
+      <c r="E87" s="25" t="s">
         <v>524</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>533</v>
       </c>
-      <c r="G87" s="72" t="s">
+      <c r="G87" s="67" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A88" s="88"/>
-      <c r="B88" s="99"/>
-      <c r="C88" s="105"/>
-      <c r="D88" s="104" t="s">
+    <row r="88" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A88" s="83"/>
+      <c r="B88" s="89"/>
+      <c r="C88" s="99"/>
+      <c r="D88" s="96" t="s">
         <v>544</v>
       </c>
-      <c r="E88" s="30">
+      <c r="E88" s="25">
         <v>90</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>536</v>
       </c>
-      <c r="G88" s="60" t="s">
+      <c r="G88" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A89" s="88"/>
-      <c r="B89" s="99"/>
-      <c r="C89" s="105"/>
-      <c r="D89" s="105"/>
-      <c r="E89" s="30">
+    <row r="89" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A89" s="83"/>
+      <c r="B89" s="89"/>
+      <c r="C89" s="99"/>
+      <c r="D89" s="99"/>
+      <c r="E89" s="25">
         <v>91</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>537</v>
       </c>
-      <c r="G89" s="60" t="s">
+      <c r="G89" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" s="88"/>
-      <c r="B90" s="99"/>
-      <c r="C90" s="105"/>
-      <c r="D90" s="105"/>
-      <c r="E90" s="30">
+    <row r="90" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A90" s="83"/>
+      <c r="B90" s="89"/>
+      <c r="C90" s="99"/>
+      <c r="D90" s="99"/>
+      <c r="E90" s="25">
         <v>92</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="G90" s="60" t="s">
+      <c r="G90" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" s="88"/>
-      <c r="B91" s="99"/>
-      <c r="C91" s="105"/>
-      <c r="D91" s="105"/>
-      <c r="E91" s="30">
+    <row r="91" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A91" s="83"/>
+      <c r="B91" s="89"/>
+      <c r="C91" s="99"/>
+      <c r="D91" s="99"/>
+      <c r="E91" s="25">
         <v>93</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="G91" s="60" t="s">
+      <c r="G91" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" s="88"/>
-      <c r="B92" s="99"/>
-      <c r="C92" s="105"/>
-      <c r="D92" s="105"/>
-      <c r="E92" s="30">
+    <row r="92" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A92" s="83"/>
+      <c r="B92" s="89"/>
+      <c r="C92" s="99"/>
+      <c r="D92" s="99"/>
+      <c r="E92" s="25">
         <v>94</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>540</v>
       </c>
-      <c r="G92" s="60" t="s">
+      <c r="G92" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" s="88"/>
-      <c r="B93" s="99"/>
-      <c r="C93" s="105"/>
-      <c r="D93" s="105"/>
-      <c r="E93" s="30">
+    <row r="93" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A93" s="83"/>
+      <c r="B93" s="89"/>
+      <c r="C93" s="99"/>
+      <c r="D93" s="99"/>
+      <c r="E93" s="25">
         <v>95</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>541</v>
       </c>
-      <c r="G93" s="60" t="s">
+      <c r="G93" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A94" s="88"/>
-      <c r="B94" s="99"/>
-      <c r="C94" s="105"/>
-      <c r="D94" s="106"/>
-      <c r="E94" s="30">
+    <row r="94" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A94" s="83"/>
+      <c r="B94" s="89"/>
+      <c r="C94" s="99"/>
+      <c r="D94" s="97"/>
+      <c r="E94" s="25">
         <v>99</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>542</v>
       </c>
-      <c r="G94" s="72" t="s">
+      <c r="G94" s="67" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A95" s="88"/>
-      <c r="B95" s="99"/>
-      <c r="C95" s="105"/>
-      <c r="D95" s="101" t="s">
+    <row r="95" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A95" s="83"/>
+      <c r="B95" s="89"/>
+      <c r="C95" s="99"/>
+      <c r="D95" s="100" t="s">
         <v>554</v>
       </c>
-      <c r="E95" s="37" t="s">
+      <c r="E95" s="32" t="s">
         <v>636</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>547</v>
       </c>
-      <c r="G95" s="60" t="s">
+      <c r="G95" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="88"/>
-      <c r="B96" s="99"/>
-      <c r="C96" s="105"/>
-      <c r="D96" s="102"/>
-      <c r="E96" s="38" t="s">
+    <row r="96" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A96" s="83"/>
+      <c r="B96" s="89"/>
+      <c r="C96" s="99"/>
+      <c r="D96" s="101"/>
+      <c r="E96" s="33" t="s">
         <v>637</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>548</v>
       </c>
-      <c r="G96" s="60" t="s">
+      <c r="G96" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A97" s="88"/>
-      <c r="B97" s="99"/>
-      <c r="C97" s="105"/>
-      <c r="D97" s="102"/>
-      <c r="E97" s="11" t="s">
+    <row r="97" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A97" s="83"/>
+      <c r="B97" s="89"/>
+      <c r="C97" s="99"/>
+      <c r="D97" s="101"/>
+      <c r="E97" s="10" t="s">
         <v>545</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>549</v>
       </c>
-      <c r="G97" s="68" t="s">
+      <c r="G97" s="63" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A98" s="88"/>
-      <c r="B98" s="99"/>
-      <c r="C98" s="105"/>
-      <c r="D98" s="102"/>
-      <c r="E98" s="11" t="s">
+    <row r="98" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A98" s="83"/>
+      <c r="B98" s="89"/>
+      <c r="C98" s="99"/>
+      <c r="D98" s="101"/>
+      <c r="E98" s="10" t="s">
         <v>546</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>550</v>
       </c>
-      <c r="G98" s="60" t="s">
+      <c r="G98" s="55" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="88"/>
-      <c r="B99" s="99"/>
-      <c r="C99" s="105"/>
-      <c r="D99" s="102"/>
-      <c r="E99" s="39" t="s">
+    <row r="99" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A99" s="83"/>
+      <c r="B99" s="89"/>
+      <c r="C99" s="99"/>
+      <c r="D99" s="101"/>
+      <c r="E99" s="34" t="s">
         <v>638</v>
       </c>
-      <c r="F99" s="24" t="s">
+      <c r="F99" s="6" t="s">
         <v>551</v>
       </c>
-      <c r="G99" s="67" t="s">
+      <c r="G99" s="62" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A100" s="88"/>
-      <c r="B100" s="99"/>
-      <c r="C100" s="105"/>
-      <c r="D100" s="103"/>
-      <c r="E100" s="37" t="s">
+    <row r="100" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A100" s="83"/>
+      <c r="B100" s="89"/>
+      <c r="C100" s="99"/>
+      <c r="D100" s="102"/>
+      <c r="E100" s="32" t="s">
         <v>639</v>
       </c>
-      <c r="F100" s="23" t="s">
+      <c r="F100" s="21" t="s">
         <v>552</v>
       </c>
-      <c r="G100" s="73" t="s">
+      <c r="G100" s="68" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A101" s="88"/>
-      <c r="B101" s="99"/>
-      <c r="C101" s="105"/>
-      <c r="D101" s="101" t="s">
+    <row r="101" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A101" s="83"/>
+      <c r="B101" s="89"/>
+      <c r="C101" s="99"/>
+      <c r="D101" s="100" t="s">
         <v>564</v>
       </c>
-      <c r="E101" s="11" t="s">
+      <c r="E101" s="10" t="s">
         <v>555</v>
       </c>
-      <c r="F101" s="23" t="s">
+      <c r="F101" s="21" t="s">
         <v>559</v>
       </c>
-      <c r="G101" s="60" t="s">
+      <c r="G101" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A102" s="88"/>
-      <c r="B102" s="99"/>
-      <c r="C102" s="105"/>
-      <c r="D102" s="102"/>
-      <c r="E102" s="11" t="s">
+    <row r="102" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A102" s="83"/>
+      <c r="B102" s="89"/>
+      <c r="C102" s="99"/>
+      <c r="D102" s="101"/>
+      <c r="E102" s="10" t="s">
         <v>556</v>
       </c>
-      <c r="F102" s="23" t="s">
+      <c r="F102" s="21" t="s">
         <v>560</v>
       </c>
-      <c r="G102" s="61" t="s">
+      <c r="G102" s="56" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A103" s="88"/>
-      <c r="B103" s="99"/>
-      <c r="C103" s="105"/>
-      <c r="D103" s="102"/>
-      <c r="E103" s="11" t="s">
+    <row r="103" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A103" s="83"/>
+      <c r="B103" s="89"/>
+      <c r="C103" s="99"/>
+      <c r="D103" s="101"/>
+      <c r="E103" s="10" t="s">
         <v>557</v>
       </c>
-      <c r="F103" s="23" t="s">
+      <c r="F103" s="21" t="s">
         <v>562</v>
       </c>
-      <c r="G103" s="60" t="s">
+      <c r="G103" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A104" s="88"/>
-      <c r="B104" s="99"/>
-      <c r="C104" s="105"/>
-      <c r="D104" s="103"/>
-      <c r="E104" s="11" t="s">
+    <row r="104" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A104" s="83"/>
+      <c r="B104" s="89"/>
+      <c r="C104" s="99"/>
+      <c r="D104" s="102"/>
+      <c r="E104" s="10" t="s">
         <v>558</v>
       </c>
-      <c r="F104" s="23" t="s">
+      <c r="F104" s="21" t="s">
         <v>563</v>
       </c>
-      <c r="G104" s="60" t="s">
+      <c r="G104" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="A105" s="88"/>
-      <c r="B105" s="99"/>
-      <c r="C105" s="105"/>
-      <c r="D105" s="101" t="s">
+    <row r="105" spans="1:7" ht="20.5" x14ac:dyDescent="0.35">
+      <c r="A105" s="83"/>
+      <c r="B105" s="89"/>
+      <c r="C105" s="99"/>
+      <c r="D105" s="100" t="s">
         <v>585</v>
       </c>
-      <c r="E105" s="11" t="s">
+      <c r="E105" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="F105" s="24" t="s">
+      <c r="F105" s="6" t="s">
         <v>575</v>
       </c>
-      <c r="G105" s="63" t="s">
+      <c r="G105" s="58" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A106" s="88"/>
-      <c r="B106" s="99"/>
-      <c r="C106" s="105"/>
-      <c r="D106" s="102"/>
-      <c r="E106" s="11" t="s">
+    <row r="106" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A106" s="83"/>
+      <c r="B106" s="89"/>
+      <c r="C106" s="99"/>
+      <c r="D106" s="101"/>
+      <c r="E106" s="10" t="s">
         <v>566</v>
       </c>
-      <c r="F106" s="23" t="s">
+      <c r="F106" s="21" t="s">
         <v>576</v>
       </c>
-      <c r="G106" s="60" t="s">
+      <c r="G106" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="88"/>
-      <c r="B107" s="99"/>
-      <c r="C107" s="105"/>
-      <c r="D107" s="102"/>
-      <c r="E107" s="11" t="s">
+    <row r="107" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A107" s="83"/>
+      <c r="B107" s="89"/>
+      <c r="C107" s="99"/>
+      <c r="D107" s="101"/>
+      <c r="E107" s="10" t="s">
         <v>567</v>
       </c>
-      <c r="F107" s="23" t="s">
+      <c r="F107" s="21" t="s">
         <v>577</v>
       </c>
-      <c r="G107" s="60" t="s">
+      <c r="G107" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="33.75" x14ac:dyDescent="0.25">
-      <c r="A108" s="88"/>
-      <c r="B108" s="99"/>
-      <c r="C108" s="105"/>
-      <c r="D108" s="102"/>
-      <c r="E108" s="11" t="s">
+    <row r="108" spans="1:7" ht="35" x14ac:dyDescent="0.35">
+      <c r="A108" s="83"/>
+      <c r="B108" s="89"/>
+      <c r="C108" s="99"/>
+      <c r="D108" s="101"/>
+      <c r="E108" s="10" t="s">
         <v>568</v>
       </c>
-      <c r="F108" s="24" t="s">
+      <c r="F108" s="6" t="s">
         <v>578</v>
       </c>
-      <c r="G108" s="61" t="s">
+      <c r="G108" s="56" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="88"/>
-      <c r="B109" s="99"/>
-      <c r="C109" s="105"/>
-      <c r="D109" s="102"/>
-      <c r="E109" s="11" t="s">
+    <row r="109" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A109" s="83"/>
+      <c r="B109" s="89"/>
+      <c r="C109" s="99"/>
+      <c r="D109" s="101"/>
+      <c r="E109" s="10" t="s">
         <v>569</v>
       </c>
-      <c r="F109" s="23" t="s">
+      <c r="F109" s="21" t="s">
         <v>579</v>
       </c>
-      <c r="G109" s="60" t="s">
+      <c r="G109" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A110" s="88"/>
-      <c r="B110" s="99"/>
-      <c r="C110" s="105"/>
-      <c r="D110" s="102"/>
-      <c r="E110" s="11" t="s">
+    <row r="110" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A110" s="83"/>
+      <c r="B110" s="89"/>
+      <c r="C110" s="99"/>
+      <c r="D110" s="101"/>
+      <c r="E110" s="10" t="s">
         <v>570</v>
       </c>
-      <c r="F110" s="23" t="s">
+      <c r="F110" s="21" t="s">
         <v>580</v>
       </c>
-      <c r="G110" s="61" t="s">
+      <c r="G110" s="56" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A111" s="88"/>
-      <c r="B111" s="99"/>
-      <c r="C111" s="105"/>
-      <c r="D111" s="102"/>
-      <c r="E111" s="11" t="s">
+    <row r="111" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A111" s="83"/>
+      <c r="B111" s="89"/>
+      <c r="C111" s="99"/>
+      <c r="D111" s="101"/>
+      <c r="E111" s="10" t="s">
         <v>571</v>
       </c>
-      <c r="F111" s="23" t="s">
+      <c r="F111" s="21" t="s">
         <v>581</v>
       </c>
-      <c r="G111" s="60" t="s">
+      <c r="G111" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A112" s="88"/>
-      <c r="B112" s="99"/>
-      <c r="C112" s="105"/>
-      <c r="D112" s="102"/>
-      <c r="E112" s="11" t="s">
+    <row r="112" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A112" s="83"/>
+      <c r="B112" s="89"/>
+      <c r="C112" s="99"/>
+      <c r="D112" s="101"/>
+      <c r="E112" s="10" t="s">
         <v>572</v>
       </c>
-      <c r="F112" s="23" t="s">
+      <c r="F112" s="21" t="s">
         <v>582</v>
       </c>
-      <c r="G112" s="60" t="s">
+      <c r="G112" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="88"/>
-      <c r="B113" s="99"/>
-      <c r="C113" s="105"/>
-      <c r="D113" s="102"/>
-      <c r="E113" s="11" t="s">
+    <row r="113" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A113" s="83"/>
+      <c r="B113" s="89"/>
+      <c r="C113" s="99"/>
+      <c r="D113" s="101"/>
+      <c r="E113" s="10" t="s">
         <v>573</v>
       </c>
-      <c r="F113" s="23" t="s">
+      <c r="F113" s="21" t="s">
         <v>583</v>
       </c>
-      <c r="G113" s="60" t="s">
+      <c r="G113" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A114" s="88"/>
-      <c r="B114" s="99"/>
-      <c r="C114" s="105"/>
-      <c r="D114" s="103"/>
-      <c r="E114" s="11" t="s">
+    <row r="114" spans="1:7" ht="30" x14ac:dyDescent="0.35">
+      <c r="A114" s="83"/>
+      <c r="B114" s="89"/>
+      <c r="C114" s="99"/>
+      <c r="D114" s="102"/>
+      <c r="E114" s="10" t="s">
         <v>574</v>
       </c>
-      <c r="F114" s="23" t="s">
+      <c r="F114" s="21" t="s">
         <v>584</v>
       </c>
-      <c r="G114" s="60" t="s">
+      <c r="G114" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A115" s="88"/>
-      <c r="B115" s="99"/>
-      <c r="C115" s="105"/>
-      <c r="D115" s="101" t="s">
+    <row r="115" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A115" s="83"/>
+      <c r="B115" s="89"/>
+      <c r="C115" s="99"/>
+      <c r="D115" s="100" t="s">
         <v>594</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="10" t="s">
         <v>586</v>
       </c>
-      <c r="F115" s="23" t="s">
+      <c r="F115" s="21" t="s">
         <v>587</v>
       </c>
-      <c r="G115" s="60" t="s">
+      <c r="G115" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A116" s="88"/>
-      <c r="B116" s="99"/>
-      <c r="C116" s="105"/>
-      <c r="D116" s="102"/>
-      <c r="E116" s="11" t="s">
+    <row r="116" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A116" s="83"/>
+      <c r="B116" s="89"/>
+      <c r="C116" s="99"/>
+      <c r="D116" s="101"/>
+      <c r="E116" s="10" t="s">
         <v>588</v>
       </c>
-      <c r="F116" s="23" t="s">
+      <c r="F116" s="21" t="s">
         <v>589</v>
       </c>
-      <c r="G116" s="60" t="s">
+      <c r="G116" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A117" s="88"/>
-      <c r="B117" s="99"/>
-      <c r="C117" s="105"/>
-      <c r="D117" s="102"/>
-      <c r="E117" s="11" t="s">
+    <row r="117" spans="1:7" ht="17" x14ac:dyDescent="0.35">
+      <c r="A117" s="83"/>
+      <c r="B117" s="89"/>
+      <c r="C117" s="99"/>
+      <c r="D117" s="101"/>
+      <c r="E117" s="10" t="s">
         <v>590</v>
       </c>
-      <c r="F117" s="23" t="s">
+      <c r="F117" s="21" t="s">
         <v>591</v>
       </c>
-      <c r="G117" s="61" t="s">
+      <c r="G117" s="56" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A118" s="88"/>
-      <c r="B118" s="99"/>
-      <c r="C118" s="105"/>
-      <c r="D118" s="103"/>
-      <c r="E118" s="11" t="s">
+    <row r="118" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A118" s="83"/>
+      <c r="B118" s="89"/>
+      <c r="C118" s="99"/>
+      <c r="D118" s="102"/>
+      <c r="E118" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="F118" s="23" t="s">
+      <c r="F118" s="21" t="s">
         <v>593</v>
       </c>
-      <c r="G118" s="60" t="s">
+      <c r="G118" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A119" s="88"/>
-      <c r="B119" s="99"/>
-      <c r="C119" s="105"/>
-      <c r="D119" s="101" t="s">
+    <row r="119" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A119" s="83"/>
+      <c r="B119" s="89"/>
+      <c r="C119" s="99"/>
+      <c r="D119" s="100" t="s">
         <v>601</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="10" t="s">
         <v>595</v>
       </c>
-      <c r="F119" s="23" t="s">
+      <c r="F119" s="21" t="s">
         <v>596</v>
       </c>
-      <c r="G119" s="60" t="s">
+      <c r="G119" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A120" s="88"/>
-      <c r="B120" s="99"/>
-      <c r="C120" s="105"/>
-      <c r="D120" s="102"/>
-      <c r="E120" s="11" t="s">
+    <row r="120" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A120" s="83"/>
+      <c r="B120" s="89"/>
+      <c r="C120" s="99"/>
+      <c r="D120" s="101"/>
+      <c r="E120" s="10" t="s">
         <v>597</v>
       </c>
-      <c r="F120" s="23" t="s">
+      <c r="F120" s="21" t="s">
         <v>598</v>
       </c>
-      <c r="G120" s="60" t="s">
+      <c r="G120" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A121" s="89"/>
-      <c r="B121" s="100"/>
-      <c r="C121" s="106"/>
-      <c r="D121" s="103"/>
-      <c r="E121" s="11" t="s">
+    <row r="121" spans="1:7" ht="15" x14ac:dyDescent="0.35">
+      <c r="A121" s="84"/>
+      <c r="B121" s="90"/>
+      <c r="C121" s="97"/>
+      <c r="D121" s="102"/>
+      <c r="E121" s="10" t="s">
         <v>599</v>
       </c>
-      <c r="F121" s="23" t="s">
+      <c r="F121" s="21" t="s">
         <v>600</v>
       </c>
-      <c r="G121" s="60" t="s">
+      <c r="G121" s="55" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A122" s="54">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" s="49">
         <v>12</v>
       </c>
-      <c r="B122" s="9" t="s">
+      <c r="B122" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>136</v>
       </c>
       <c r="D122" s="4"/>
-      <c r="E122" s="30"/>
+      <c r="E122" s="25"/>
       <c r="F122" s="6"/>
-      <c r="G122" s="55"/>
-    </row>
-    <row r="123" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A123" s="87">
+      <c r="G122" s="50"/>
+    </row>
+    <row r="123" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A123" s="82">
         <v>13</v>
       </c>
-      <c r="B123" s="98" t="s">
+      <c r="B123" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="C123" s="95" t="s">
+      <c r="C123" s="85" t="s">
         <v>368</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="E123" s="30" t="s">
+      <c r="E123" s="25" t="s">
         <v>369</v>
       </c>
-      <c r="F123" s="18" t="s">
+      <c r="F123" s="17" t="s">
         <v>683</v>
       </c>
-      <c r="G123" s="55"/>
-    </row>
-    <row r="124" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A124" s="88"/>
-      <c r="B124" s="99"/>
-      <c r="C124" s="96"/>
+      <c r="G123" s="50"/>
+    </row>
+    <row r="124" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A124" s="83"/>
+      <c r="B124" s="89"/>
+      <c r="C124" s="86"/>
       <c r="D124" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="E124" s="30" t="s">
+      <c r="E124" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="F124" s="18" t="s">
+      <c r="F124" s="17" t="s">
         <v>684</v>
       </c>
-      <c r="G124" s="55"/>
-    </row>
-    <row r="125" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A125" s="89"/>
-      <c r="B125" s="100"/>
-      <c r="C125" s="97"/>
+      <c r="G124" s="50"/>
+    </row>
+    <row r="125" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A125" s="84"/>
+      <c r="B125" s="90"/>
+      <c r="C125" s="87"/>
       <c r="D125" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="E125" s="30" t="s">
+      <c r="E125" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="F125" s="18" t="s">
+      <c r="F125" s="17" t="s">
         <v>685</v>
       </c>
-      <c r="G125" s="55"/>
-    </row>
-    <row r="126" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A126" s="54">
+      <c r="G125" s="50"/>
+    </row>
+    <row r="126" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A126" s="49">
         <v>14</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>137</v>
       </c>
       <c r="D126" s="4"/>
-      <c r="E126" s="30"/>
+      <c r="E126" s="25"/>
       <c r="F126" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="G126" s="55"/>
-    </row>
-    <row r="127" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A127" s="54">
+      <c r="G126" s="50"/>
+    </row>
+    <row r="127" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A127" s="49">
         <v>15</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>138</v>
       </c>
       <c r="D127" s="4"/>
-      <c r="E127" s="30"/>
+      <c r="E127" s="25"/>
       <c r="F127" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="G127" s="55"/>
-    </row>
-    <row r="128" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A128" s="110">
+      <c r="G127" s="50"/>
+    </row>
+    <row r="128" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A128" s="103">
         <v>16</v>
       </c>
-      <c r="B128" s="112" t="s">
+      <c r="B128" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C128" s="111" t="s">
+      <c r="C128" s="98" t="s">
         <v>296</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="E128" s="30" t="s">
+      <c r="E128" s="25" t="s">
         <v>234</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>646</v>
       </c>
-      <c r="G128" s="55"/>
-    </row>
-    <row r="129" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A129" s="110"/>
-      <c r="B129" s="112"/>
-      <c r="C129" s="111"/>
+      <c r="G128" s="50"/>
+    </row>
+    <row r="129" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A129" s="103"/>
+      <c r="B129" s="104"/>
+      <c r="C129" s="98"/>
       <c r="D129" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="E129" s="30" t="s">
+      <c r="E129" s="25" t="s">
         <v>292</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="G129" s="55"/>
-    </row>
-    <row r="130" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A130" s="110"/>
-      <c r="B130" s="112"/>
-      <c r="C130" s="111"/>
+      <c r="G129" s="50"/>
+    </row>
+    <row r="130" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A130" s="103"/>
+      <c r="B130" s="104"/>
+      <c r="C130" s="98"/>
       <c r="D130" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="E130" s="22" t="s">
+      <c r="E130" s="20" t="s">
         <v>702</v>
       </c>
-      <c r="F130" s="19" t="s">
+      <c r="F130" s="18" t="s">
         <v>701</v>
       </c>
-      <c r="G130" s="55"/>
-    </row>
-    <row r="131" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A131" s="110"/>
-      <c r="B131" s="112"/>
-      <c r="C131" s="111"/>
+      <c r="G130" s="50"/>
+    </row>
+    <row r="131" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A131" s="103"/>
+      <c r="B131" s="104"/>
+      <c r="C131" s="98"/>
       <c r="D131" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="E131" s="22" t="s">
+      <c r="E131" s="20" t="s">
         <v>705</v>
       </c>
-      <c r="F131" s="19" t="s">
+      <c r="F131" s="18" t="s">
         <v>706</v>
       </c>
-      <c r="G131" s="55"/>
-    </row>
-    <row r="132" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A132" s="110"/>
-      <c r="B132" s="112"/>
-      <c r="C132" s="111"/>
+      <c r="G131" s="50"/>
+    </row>
+    <row r="132" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A132" s="103"/>
+      <c r="B132" s="104"/>
+      <c r="C132" s="98"/>
       <c r="D132" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="E132" s="30" t="s">
+      <c r="E132" s="25" t="s">
         <v>707</v>
       </c>
-      <c r="F132" s="19" t="s">
+      <c r="F132" s="18" t="s">
         <v>708</v>
       </c>
-      <c r="G132" s="55"/>
-    </row>
-    <row r="133" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A133" s="110"/>
-      <c r="B133" s="112"/>
-      <c r="C133" s="111"/>
+      <c r="G132" s="50"/>
+    </row>
+    <row r="133" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A133" s="103"/>
+      <c r="B133" s="104"/>
+      <c r="C133" s="98"/>
       <c r="D133" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E133" s="30" t="s">
+      <c r="E133" s="25" t="s">
         <v>293</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>648</v>
       </c>
-      <c r="G133" s="55"/>
-    </row>
-    <row r="134" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A134" s="110"/>
-      <c r="B134" s="112"/>
-      <c r="C134" s="111"/>
-      <c r="D134" s="21" t="s">
+      <c r="G133" s="50"/>
+    </row>
+    <row r="134" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A134" s="103"/>
+      <c r="B134" s="104"/>
+      <c r="C134" s="98"/>
+      <c r="D134" s="19" t="s">
         <v>711</v>
       </c>
-      <c r="E134" s="30" t="s">
+      <c r="E134" s="25" t="s">
         <v>712</v>
       </c>
-      <c r="F134" s="19" t="s">
+      <c r="F134" s="18" t="s">
         <v>713</v>
       </c>
-      <c r="G134" s="55"/>
-    </row>
-    <row r="135" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A135" s="110"/>
-      <c r="B135" s="112"/>
-      <c r="C135" s="111"/>
+      <c r="G134" s="50"/>
+    </row>
+    <row r="135" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A135" s="103"/>
+      <c r="B135" s="104"/>
+      <c r="C135" s="98"/>
       <c r="D135" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="E135" s="30" t="s">
+      <c r="E135" s="25" t="s">
         <v>294</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>649</v>
       </c>
-      <c r="G135" s="55"/>
-    </row>
-    <row r="136" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A136" s="110"/>
-      <c r="B136" s="112"/>
-      <c r="C136" s="111"/>
+      <c r="G135" s="50"/>
+    </row>
+    <row r="136" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A136" s="103"/>
+      <c r="B136" s="104"/>
+      <c r="C136" s="98"/>
       <c r="D136" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="E136" s="30" t="s">
+      <c r="E136" s="25" t="s">
         <v>710</v>
       </c>
-      <c r="F136" s="19" t="s">
+      <c r="F136" s="18" t="s">
         <v>709</v>
       </c>
-      <c r="G136" s="55"/>
-    </row>
-    <row r="137" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A137" s="110"/>
-      <c r="B137" s="112"/>
-      <c r="C137" s="111"/>
+      <c r="G136" s="50"/>
+    </row>
+    <row r="137" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A137" s="103"/>
+      <c r="B137" s="104"/>
+      <c r="C137" s="98"/>
       <c r="D137" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="E137" s="22" t="s">
+      <c r="E137" s="20" t="s">
         <v>703</v>
       </c>
-      <c r="F137" s="19" t="s">
+      <c r="F137" s="18" t="s">
         <v>704</v>
       </c>
-      <c r="G137" s="55"/>
-    </row>
-    <row r="138" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A138" s="110"/>
-      <c r="B138" s="112"/>
-      <c r="C138" s="111"/>
+      <c r="G137" s="50"/>
+    </row>
+    <row r="138" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A138" s="103"/>
+      <c r="B138" s="104"/>
+      <c r="C138" s="98"/>
       <c r="D138" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="E138" s="30" t="s">
+      <c r="E138" s="25" t="s">
         <v>295</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="G138" s="55"/>
-    </row>
-    <row r="139" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A139" s="54">
+      <c r="G138" s="50"/>
+    </row>
+    <row r="139" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A139" s="49">
         <v>17</v>
       </c>
-      <c r="B139" s="9" t="s">
+      <c r="B139" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>139</v>
       </c>
       <c r="D139" s="4"/>
-      <c r="E139" s="30"/>
+      <c r="E139" s="25"/>
       <c r="F139" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="G139" s="74"/>
-    </row>
-    <row r="140" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A140" s="54">
+      <c r="G139" s="69"/>
+    </row>
+    <row r="140" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A140" s="49">
         <v>18</v>
       </c>
-      <c r="B140" s="9" t="s">
+      <c r="B140" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C140" s="4" t="s">
         <v>140</v>
       </c>
       <c r="D140" s="4"/>
-      <c r="E140" s="30"/>
+      <c r="E140" s="25"/>
       <c r="F140" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G140" s="55"/>
-    </row>
-    <row r="141" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A141" s="87">
+      <c r="G140" s="50"/>
+    </row>
+    <row r="141" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A141" s="82">
         <v>19</v>
       </c>
-      <c r="B141" s="98" t="s">
+      <c r="B141" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="C141" s="104" t="s">
+      <c r="C141" s="96" t="s">
         <v>305</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="E141" s="30"/>
+      <c r="E141" s="25"/>
       <c r="F141" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="G141" s="55"/>
-    </row>
-    <row r="142" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A142" s="89"/>
-      <c r="B142" s="100"/>
-      <c r="C142" s="106"/>
+      <c r="G141" s="50"/>
+    </row>
+    <row r="142" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A142" s="84"/>
+      <c r="B142" s="90"/>
+      <c r="C142" s="97"/>
       <c r="D142" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="E142" s="30"/>
+      <c r="E142" s="25"/>
       <c r="F142" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="G142" s="55"/>
-    </row>
-    <row r="143" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A143" s="54">
+      <c r="G142" s="50"/>
+    </row>
+    <row r="143" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A143" s="49">
         <v>20</v>
       </c>
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>141</v>
       </c>
       <c r="D143" s="4"/>
-      <c r="E143" s="30"/>
+      <c r="E143" s="25"/>
       <c r="F143" s="1" t="s">
         <v>690</v>
       </c>
-      <c r="G143" s="55"/>
-    </row>
-    <row r="144" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A144" s="54">
+      <c r="G143" s="50"/>
+    </row>
+    <row r="144" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A144" s="49">
         <v>21</v>
       </c>
-      <c r="B144" s="9" t="s">
+      <c r="B144" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>142</v>
       </c>
       <c r="D144" s="4"/>
-      <c r="E144" s="30"/>
+      <c r="E144" s="25"/>
       <c r="F144" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="G144" s="55"/>
-    </row>
-    <row r="145" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A145" s="54">
+      <c r="G144" s="50"/>
+    </row>
+    <row r="145" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A145" s="49">
         <v>22</v>
       </c>
-      <c r="B145" s="9" t="s">
+      <c r="B145" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>143</v>
       </c>
       <c r="D145" s="4"/>
-      <c r="E145" s="30"/>
+      <c r="E145" s="25"/>
       <c r="F145" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="G145" s="55"/>
-    </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="87">
+      <c r="G145" s="50"/>
+    </row>
+    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="82">
         <v>23</v>
       </c>
-      <c r="B146" s="98" t="s">
+      <c r="B146" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="C146" s="95" t="s">
+      <c r="C146" s="85" t="s">
         <v>302</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E146" s="30" t="s">
+      <c r="E146" s="25" t="s">
         <v>300</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G146" s="55"/>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A147" s="88"/>
-      <c r="B147" s="99"/>
-      <c r="C147" s="96"/>
+      <c r="G146" s="50"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A147" s="83"/>
+      <c r="B147" s="89"/>
+      <c r="C147" s="86"/>
       <c r="D147" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E147" s="30" t="s">
+      <c r="E147" s="25" t="s">
         <v>301</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="G147" s="55"/>
-    </row>
-    <row r="148" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A148" s="88"/>
-      <c r="B148" s="99"/>
-      <c r="C148" s="96"/>
+      <c r="G147" s="50"/>
+    </row>
+    <row r="148" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A148" s="83"/>
+      <c r="B148" s="89"/>
+      <c r="C148" s="86"/>
       <c r="D148" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="E148" s="30" t="s">
+      <c r="E148" s="25" t="s">
         <v>340</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="G148" s="55"/>
-    </row>
-    <row r="149" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A149" s="88"/>
-      <c r="B149" s="99"/>
-      <c r="C149" s="96"/>
+      <c r="G148" s="50"/>
+    </row>
+    <row r="149" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A149" s="83"/>
+      <c r="B149" s="89"/>
+      <c r="C149" s="86"/>
       <c r="D149" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="E149" s="30" t="s">
+      <c r="E149" s="25" t="s">
         <v>342</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="G149" s="55"/>
-    </row>
-    <row r="150" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A150" s="89"/>
-      <c r="B150" s="100"/>
-      <c r="C150" s="97"/>
+      <c r="G149" s="50"/>
+    </row>
+    <row r="150" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A150" s="84"/>
+      <c r="B150" s="90"/>
+      <c r="C150" s="87"/>
       <c r="D150" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E150" s="30" t="s">
+      <c r="E150" s="25" t="s">
         <v>338</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="G150" s="55"/>
-    </row>
-    <row r="151" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A151" s="87">
+      <c r="G150" s="50"/>
+    </row>
+    <row r="151" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A151" s="82">
         <v>24</v>
       </c>
-      <c r="B151" s="98" t="s">
+      <c r="B151" s="88" t="s">
         <v>23</v>
       </c>
-      <c r="C151" s="95" t="s">
+      <c r="C151" s="85" t="s">
         <v>299</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E151" s="30" t="s">
+      <c r="E151" s="25" t="s">
         <v>640</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G151" s="55"/>
-    </row>
-    <row r="152" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A152" s="88"/>
-      <c r="B152" s="99"/>
-      <c r="C152" s="96"/>
+      <c r="G151" s="50"/>
+    </row>
+    <row r="152" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A152" s="83"/>
+      <c r="B152" s="89"/>
+      <c r="C152" s="86"/>
       <c r="D152" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="E152" s="30" t="s">
+      <c r="E152" s="25" t="s">
         <v>297</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G152" s="55"/>
-    </row>
-    <row r="153" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A153" s="89"/>
-      <c r="B153" s="100"/>
-      <c r="C153" s="97"/>
+      <c r="G152" s="50"/>
+    </row>
+    <row r="153" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A153" s="84"/>
+      <c r="B153" s="90"/>
+      <c r="C153" s="87"/>
       <c r="D153" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E153" s="30" t="s">
+      <c r="E153" s="25" t="s">
         <v>298</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="G153" s="55"/>
-    </row>
-    <row r="154" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A154" s="54">
+      <c r="G153" s="50"/>
+    </row>
+    <row r="154" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A154" s="49">
         <v>25</v>
       </c>
-      <c r="B154" s="9" t="s">
+      <c r="B154" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C154" s="4" t="s">
         <v>144</v>
       </c>
       <c r="D154" s="4"/>
-      <c r="E154" s="30"/>
+      <c r="E154" s="25"/>
       <c r="F154" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="G154" s="55"/>
-    </row>
-    <row r="155" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A155" s="54">
+      <c r="G154" s="50"/>
+    </row>
+    <row r="155" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A155" s="49">
         <v>26</v>
       </c>
-      <c r="B155" s="9" t="s">
+      <c r="B155" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C155" s="4" t="s">
         <v>145</v>
       </c>
       <c r="D155" s="4"/>
-      <c r="E155" s="30"/>
+      <c r="E155" s="25"/>
       <c r="F155" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="G155" s="55"/>
-    </row>
-    <row r="156" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A156" s="54">
+      <c r="G155" s="50"/>
+    </row>
+    <row r="156" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A156" s="49">
         <v>27</v>
       </c>
-      <c r="B156" s="9" t="s">
+      <c r="B156" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C156" s="4" t="s">
         <v>146</v>
       </c>
       <c r="D156" s="4"/>
-      <c r="E156" s="30"/>
+      <c r="E156" s="25"/>
       <c r="F156" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G156" s="55"/>
-    </row>
-    <row r="157" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A157" s="54">
+      <c r="G156" s="50"/>
+    </row>
+    <row r="157" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A157" s="49">
         <v>28</v>
       </c>
-      <c r="B157" s="9" t="s">
+      <c r="B157" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>147</v>
       </c>
       <c r="D157" s="4"/>
-      <c r="E157" s="30"/>
+      <c r="E157" s="25"/>
       <c r="F157" s="1" t="s">
         <v>660</v>
       </c>
-      <c r="G157" s="55"/>
-    </row>
-    <row r="158" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A158" s="54">
+      <c r="G157" s="50"/>
+    </row>
+    <row r="158" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A158" s="49">
         <v>29</v>
       </c>
-      <c r="B158" s="9" t="s">
+      <c r="B158" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D158" s="4"/>
-      <c r="E158" s="30"/>
+      <c r="E158" s="25"/>
       <c r="F158" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="G158" s="55"/>
-    </row>
-    <row r="159" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A159" s="54">
+      <c r="G158" s="50"/>
+    </row>
+    <row r="159" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A159" s="49">
         <v>30</v>
       </c>
-      <c r="B159" s="9" t="s">
+      <c r="B159" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>149</v>
       </c>
       <c r="D159" s="4"/>
-      <c r="E159" s="30"/>
+      <c r="E159" s="25"/>
       <c r="F159" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="G159" s="55"/>
-    </row>
-    <row r="160" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A160" s="54">
+      <c r="G159" s="50"/>
+    </row>
+    <row r="160" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A160" s="49">
         <v>31</v>
       </c>
-      <c r="B160" s="9" t="s">
+      <c r="B160" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C160" s="4" t="s">
         <v>150</v>
       </c>
       <c r="D160" s="4"/>
-      <c r="E160" s="30"/>
+      <c r="E160" s="25"/>
       <c r="F160" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="G160" s="55"/>
-    </row>
-    <row r="161" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A161" s="54">
+      <c r="G160" s="50"/>
+    </row>
+    <row r="161" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A161" s="49">
         <v>32</v>
       </c>
-      <c r="B161" s="9" t="s">
+      <c r="B161" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C161" s="4" t="s">
         <v>151</v>
       </c>
       <c r="D161" s="4"/>
-      <c r="E161" s="30"/>
+      <c r="E161" s="25"/>
       <c r="F161" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="G161" s="55"/>
-    </row>
-    <row r="162" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A162" s="54">
+      <c r="G161" s="50"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A162" s="49">
         <v>33</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C162" s="28" t="s">
+      <c r="C162" s="4" t="s">
         <v>152</v>
       </c>
       <c r="D162" s="4"/>
-      <c r="E162" s="22" t="s">
+      <c r="E162" s="20" t="s">
         <v>152</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="G162" s="55"/>
-    </row>
-    <row r="163" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A163" s="54">
+      <c r="G162" s="50"/>
+    </row>
+    <row r="163" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A163" s="49">
         <v>34</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C163" s="28" t="s">
+      <c r="C163" s="4" t="s">
         <v>306</v>
       </c>
       <c r="D163" s="4"/>
-      <c r="E163" s="30" t="s">
+      <c r="E163" s="25" t="s">
         <v>153</v>
       </c>
       <c r="F163" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="G163" s="55"/>
-    </row>
-    <row r="164" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A164" s="54">
+      <c r="G163" s="50"/>
+    </row>
+    <row r="164" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A164" s="49">
         <v>35</v>
       </c>
-      <c r="B164" s="9" t="s">
+      <c r="B164" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C164" s="4" t="s">
         <v>154</v>
       </c>
       <c r="D164" s="4"/>
-      <c r="E164" s="30"/>
+      <c r="E164" s="25"/>
       <c r="F164" s="1" t="s">
         <v>665</v>
       </c>
-      <c r="G164" s="55"/>
-    </row>
-    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A165" s="54">
+      <c r="G164" s="50"/>
+    </row>
+    <row r="165" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A165" s="49">
         <v>36</v>
       </c>
-      <c r="B165" s="9" t="s">
+      <c r="B165" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C165" s="4" t="s">
@@ -10297,2971 +10271,2991 @@
       <c r="D165" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="E165" s="30"/>
+      <c r="E165" s="25"/>
       <c r="F165" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="G165" s="55"/>
-    </row>
-    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A166" s="54">
+      <c r="G165" s="50"/>
+    </row>
+    <row r="166" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A166" s="49">
         <v>37</v>
       </c>
-      <c r="B166" s="9" t="s">
+      <c r="B166" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>155</v>
       </c>
       <c r="D166" s="4"/>
-      <c r="E166" s="30"/>
+      <c r="E166" s="25"/>
       <c r="F166" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="G166" s="55"/>
-    </row>
-    <row r="167" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A167" s="54">
+      <c r="G166" s="50"/>
+    </row>
+    <row r="167" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A167" s="49">
         <v>38</v>
       </c>
-      <c r="B167" s="9" t="s">
+      <c r="B167" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C167" s="4" t="s">
         <v>156</v>
       </c>
       <c r="D167" s="4"/>
-      <c r="E167" s="30"/>
+      <c r="E167" s="25"/>
       <c r="F167" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="G167" s="55"/>
-    </row>
-    <row r="168" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A168" s="54">
+      <c r="G167" s="50"/>
+    </row>
+    <row r="168" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A168" s="49">
         <v>39</v>
       </c>
-      <c r="B168" s="9" t="s">
+      <c r="B168" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>157</v>
       </c>
       <c r="D168" s="4"/>
-      <c r="E168" s="30"/>
+      <c r="E168" s="25"/>
       <c r="F168" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="G168" s="55"/>
-    </row>
-    <row r="169" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A169" s="54">
+      <c r="G168" s="50"/>
+    </row>
+    <row r="169" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A169" s="49">
         <v>40</v>
       </c>
-      <c r="B169" s="9" t="s">
+      <c r="B169" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>158</v>
       </c>
       <c r="D169" s="4"/>
-      <c r="E169" s="30"/>
+      <c r="E169" s="25"/>
       <c r="F169" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="G169" s="55"/>
-    </row>
-    <row r="170" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A170" s="54">
+      <c r="G169" s="50"/>
+    </row>
+    <row r="170" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A170" s="49">
         <v>41</v>
       </c>
-      <c r="B170" s="9" t="s">
+      <c r="B170" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C170" s="4" t="s">
         <v>159</v>
       </c>
       <c r="D170" s="4"/>
-      <c r="E170" s="30"/>
+      <c r="E170" s="25"/>
       <c r="F170" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="G170" s="55"/>
-    </row>
-    <row r="171" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A171" s="54">
+      <c r="G170" s="50"/>
+    </row>
+    <row r="171" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A171" s="49">
         <v>42</v>
       </c>
-      <c r="B171" s="9" t="s">
+      <c r="B171" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>160</v>
       </c>
       <c r="D171" s="4"/>
-      <c r="E171" s="30"/>
+      <c r="E171" s="25"/>
       <c r="F171" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="G171" s="55"/>
-    </row>
-    <row r="172" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A172" s="87">
+      <c r="G171" s="50"/>
+    </row>
+    <row r="172" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A172" s="82">
         <v>43</v>
       </c>
-      <c r="B172" s="98" t="s">
+      <c r="B172" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="C172" s="104" t="s">
+      <c r="C172" s="96" t="s">
         <v>309</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="E172" s="30"/>
+      <c r="E172" s="25"/>
       <c r="F172" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="G172" s="55"/>
-    </row>
-    <row r="173" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A173" s="89"/>
-      <c r="B173" s="100"/>
-      <c r="C173" s="106"/>
+      <c r="G172" s="50"/>
+    </row>
+    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A173" s="84"/>
+      <c r="B173" s="90"/>
+      <c r="C173" s="97"/>
       <c r="D173" s="4" t="s">
         <v>308</v>
       </c>
-      <c r="E173" s="30"/>
+      <c r="E173" s="25"/>
       <c r="F173" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="G173" s="55"/>
-    </row>
-    <row r="174" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A174" s="54">
+      <c r="G173" s="50"/>
+    </row>
+    <row r="174" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A174" s="49">
         <v>44</v>
       </c>
-      <c r="B174" s="9" t="s">
+      <c r="B174" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>231</v>
       </c>
       <c r="D174" s="4"/>
-      <c r="E174" s="30"/>
+      <c r="E174" s="25"/>
       <c r="F174" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="G174" s="55"/>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A175" s="87">
+      <c r="G174" s="50"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A175" s="82">
         <v>45</v>
       </c>
-      <c r="B175" s="98" t="s">
+      <c r="B175" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="C175" s="95" t="s">
+      <c r="C175" s="85" t="s">
         <v>315</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E175" s="30" t="s">
+      <c r="E175" s="25" t="s">
         <v>303</v>
       </c>
       <c r="F175" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="G175" s="55"/>
-    </row>
-    <row r="176" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="88"/>
-      <c r="B176" s="99"/>
-      <c r="C176" s="96"/>
+      <c r="G175" s="50"/>
+    </row>
+    <row r="176" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A176" s="83"/>
+      <c r="B176" s="89"/>
+      <c r="C176" s="86"/>
       <c r="D176" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E176" s="30" t="s">
+      <c r="E176" s="25" t="s">
         <v>310</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G176" s="55"/>
-    </row>
-    <row r="177" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A177" s="88"/>
-      <c r="B177" s="99"/>
-      <c r="C177" s="96"/>
+      <c r="G176" s="50"/>
+    </row>
+    <row r="177" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A177" s="83"/>
+      <c r="B177" s="89"/>
+      <c r="C177" s="86"/>
       <c r="D177" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E177" s="30" t="s">
+      <c r="E177" s="25" t="s">
         <v>311</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="G177" s="55"/>
-    </row>
-    <row r="178" spans="1:7" ht="105" x14ac:dyDescent="0.25">
-      <c r="A178" s="88"/>
-      <c r="B178" s="99"/>
-      <c r="C178" s="96"/>
+      <c r="G177" s="50"/>
+    </row>
+    <row r="178" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A178" s="83"/>
+      <c r="B178" s="89"/>
+      <c r="C178" s="86"/>
       <c r="D178" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E178" s="30" t="s">
+      <c r="E178" s="25" t="s">
         <v>312</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>677</v>
       </c>
-      <c r="G178" s="55"/>
-    </row>
-    <row r="179" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A179" s="88"/>
-      <c r="B179" s="99"/>
-      <c r="C179" s="96"/>
+      <c r="G178" s="50"/>
+    </row>
+    <row r="179" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A179" s="83"/>
+      <c r="B179" s="89"/>
+      <c r="C179" s="86"/>
       <c r="D179" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E179" s="30" t="s">
+      <c r="E179" s="25" t="s">
         <v>313</v>
       </c>
       <c r="F179" s="6" t="s">
         <v>655</v>
       </c>
-      <c r="G179" s="55"/>
-    </row>
-    <row r="180" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A180" s="88"/>
-      <c r="B180" s="99"/>
-      <c r="C180" s="96"/>
+      <c r="G179" s="50"/>
+    </row>
+    <row r="180" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A180" s="83"/>
+      <c r="B180" s="89"/>
+      <c r="C180" s="86"/>
       <c r="D180" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E180" s="30" t="s">
+      <c r="E180" s="25" t="s">
         <v>754</v>
       </c>
-      <c r="F180" s="18" t="s">
+      <c r="F180" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="G180" s="55"/>
-    </row>
-    <row r="181" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A181" s="88"/>
-      <c r="B181" s="99"/>
-      <c r="C181" s="96"/>
+      <c r="G180" s="50"/>
+    </row>
+    <row r="181" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A181" s="83"/>
+      <c r="B181" s="89"/>
+      <c r="C181" s="86"/>
       <c r="D181" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E181" s="75" t="s">
+      <c r="E181" s="15" t="s">
         <v>756</v>
       </c>
       <c r="F181" s="6" t="s">
         <v>678</v>
       </c>
-      <c r="G181" s="55"/>
-    </row>
-    <row r="182" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A182" s="88"/>
-      <c r="B182" s="99"/>
-      <c r="C182" s="96"/>
+      <c r="G181" s="50"/>
+    </row>
+    <row r="182" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A182" s="83"/>
+      <c r="B182" s="89"/>
+      <c r="C182" s="86"/>
       <c r="D182" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E182" s="76" t="s">
+      <c r="E182" s="70" t="s">
         <v>731</v>
       </c>
-      <c r="F182" s="18" t="s">
+      <c r="F182" s="17" t="s">
         <v>732</v>
       </c>
-      <c r="G182" s="55"/>
-    </row>
-    <row r="183" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A183" s="88"/>
-      <c r="B183" s="99"/>
-      <c r="C183" s="96"/>
+      <c r="G182" s="50"/>
+    </row>
+    <row r="183" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A183" s="83"/>
+      <c r="B183" s="89"/>
+      <c r="C183" s="86"/>
       <c r="D183" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E183" s="30" t="s">
+      <c r="E183" s="25" t="s">
         <v>725</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="G183" s="55"/>
-    </row>
-    <row r="184" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A184" s="88"/>
-      <c r="B184" s="99"/>
-      <c r="C184" s="96"/>
-      <c r="D184" s="21" t="s">
+      <c r="G183" s="50"/>
+    </row>
+    <row r="184" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A184" s="83"/>
+      <c r="B184" s="89"/>
+      <c r="C184" s="86"/>
+      <c r="D184" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="E184" s="22" t="s">
+      <c r="E184" s="20" t="s">
         <v>726</v>
       </c>
-      <c r="F184" s="18" t="s">
+      <c r="F184" s="17" t="s">
         <v>734</v>
       </c>
-      <c r="G184" s="55"/>
-    </row>
-    <row r="185" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A185" s="88"/>
-      <c r="B185" s="99"/>
-      <c r="C185" s="96"/>
+      <c r="G184" s="50"/>
+    </row>
+    <row r="185" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A185" s="83"/>
+      <c r="B185" s="89"/>
+      <c r="C185" s="86"/>
       <c r="D185" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E185" s="30" t="s">
+      <c r="E185" s="25" t="s">
         <v>727</v>
       </c>
-      <c r="F185" s="18" t="s">
+      <c r="F185" s="17" t="s">
         <v>735</v>
       </c>
-      <c r="G185" s="55"/>
-    </row>
-    <row r="186" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A186" s="88"/>
-      <c r="B186" s="99"/>
-      <c r="C186" s="96"/>
+      <c r="G185" s="50"/>
+    </row>
+    <row r="186" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A186" s="83"/>
+      <c r="B186" s="89"/>
+      <c r="C186" s="86"/>
       <c r="D186" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="E186" s="30" t="s">
+      <c r="E186" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="F186" s="18" t="s">
+      <c r="F186" s="17" t="s">
         <v>736</v>
       </c>
-      <c r="G186" s="55"/>
-    </row>
-    <row r="187" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A187" s="88"/>
-      <c r="B187" s="99"/>
-      <c r="C187" s="96"/>
+      <c r="G186" s="50"/>
+    </row>
+    <row r="187" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A187" s="83"/>
+      <c r="B187" s="89"/>
+      <c r="C187" s="86"/>
       <c r="D187" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E187" s="30" t="s">
+      <c r="E187" s="25" t="s">
         <v>728</v>
       </c>
       <c r="F187" s="6" t="s">
         <v>647</v>
       </c>
-      <c r="G187" s="55"/>
-    </row>
-    <row r="188" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A188" s="88"/>
-      <c r="B188" s="99"/>
-      <c r="C188" s="96"/>
+      <c r="G187" s="50"/>
+    </row>
+    <row r="188" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A188" s="83"/>
+      <c r="B188" s="89"/>
+      <c r="C188" s="86"/>
       <c r="D188" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="E188" s="30" t="s">
+      <c r="E188" s="25" t="s">
         <v>730</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="G188" s="55"/>
-    </row>
-    <row r="189" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A189" s="88"/>
-      <c r="B189" s="99"/>
-      <c r="C189" s="96"/>
+      <c r="G188" s="50"/>
+    </row>
+    <row r="189" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A189" s="83"/>
+      <c r="B189" s="89"/>
+      <c r="C189" s="86"/>
       <c r="D189" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E189" s="30" t="s">
+      <c r="E189" s="25" t="s">
         <v>729</v>
       </c>
       <c r="F189" s="6" t="s">
         <v>650</v>
       </c>
-      <c r="G189" s="55"/>
-    </row>
-    <row r="190" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A190" s="88"/>
-      <c r="B190" s="99"/>
-      <c r="C190" s="96"/>
+      <c r="G189" s="50"/>
+    </row>
+    <row r="190" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A190" s="83"/>
+      <c r="B190" s="89"/>
+      <c r="C190" s="86"/>
       <c r="D190" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="E190" s="30" t="s">
+      <c r="E190" s="25" t="s">
         <v>758</v>
       </c>
-      <c r="F190" s="18" t="s">
+      <c r="F190" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="G190" s="55"/>
-    </row>
-    <row r="191" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A191" s="89"/>
-      <c r="B191" s="100"/>
-      <c r="C191" s="97"/>
+      <c r="G190" s="50"/>
+    </row>
+    <row r="191" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A191" s="84"/>
+      <c r="B191" s="90"/>
+      <c r="C191" s="87"/>
       <c r="D191" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E191" s="30" t="s">
+      <c r="E191" s="25" t="s">
         <v>757</v>
       </c>
       <c r="F191" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G191" s="55"/>
-    </row>
-    <row r="192" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A192" s="54">
+      <c r="G191" s="50"/>
+    </row>
+    <row r="192" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A192" s="49">
         <v>46</v>
       </c>
-      <c r="B192" s="9" t="s">
+      <c r="B192" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C192" s="4" t="s">
         <v>161</v>
       </c>
       <c r="D192" s="4"/>
-      <c r="E192" s="30"/>
+      <c r="E192" s="25"/>
       <c r="F192" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="G192" s="55"/>
-    </row>
-    <row r="193" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A193" s="54">
+      <c r="G192" s="50"/>
+    </row>
+    <row r="193" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A193" s="49">
         <v>47</v>
       </c>
-      <c r="B193" s="9" t="s">
+      <c r="B193" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C193" s="28" t="s">
+      <c r="C193" s="4" t="s">
         <v>162</v>
       </c>
       <c r="D193" s="4"/>
-      <c r="E193" s="30"/>
+      <c r="E193" s="25"/>
       <c r="F193" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G193" s="55"/>
-    </row>
-    <row r="194" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A194" s="54">
+      <c r="G193" s="50"/>
+    </row>
+    <row r="194" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A194" s="49">
         <v>48</v>
       </c>
-      <c r="B194" s="9" t="s">
+      <c r="B194" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C194" s="4" t="s">
         <v>163</v>
       </c>
       <c r="D194" s="4"/>
-      <c r="E194" s="30"/>
+      <c r="E194" s="25"/>
       <c r="F194" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="G194" s="55"/>
-    </row>
-    <row r="195" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A195" s="87">
+      <c r="G194" s="50"/>
+    </row>
+    <row r="195" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A195" s="82">
         <v>49</v>
       </c>
-      <c r="B195" s="98" t="s">
+      <c r="B195" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="C195" s="95" t="s">
+      <c r="C195" s="85" t="s">
         <v>362</v>
       </c>
       <c r="D195" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E195" s="22" t="s">
+      <c r="E195" s="20" t="s">
         <v>643</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>642</v>
       </c>
-      <c r="G195" s="55"/>
-    </row>
-    <row r="196" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A196" s="88"/>
-      <c r="B196" s="99"/>
-      <c r="C196" s="96"/>
+      <c r="G195" s="50"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A196" s="83"/>
+      <c r="B196" s="89"/>
+      <c r="C196" s="86"/>
       <c r="D196" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E196" s="22" t="s">
+      <c r="E196" s="20" t="s">
         <v>332</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="G196" s="55"/>
-    </row>
-    <row r="197" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A197" s="88"/>
-      <c r="B197" s="99"/>
-      <c r="C197" s="96"/>
+      <c r="G196" s="50"/>
+    </row>
+    <row r="197" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A197" s="83"/>
+      <c r="B197" s="89"/>
+      <c r="C197" s="86"/>
       <c r="D197" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E197" s="30" t="s">
+      <c r="E197" s="25" t="s">
         <v>333</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>680</v>
       </c>
-      <c r="G197" s="55"/>
-    </row>
-    <row r="198" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A198" s="88"/>
-      <c r="B198" s="99"/>
-      <c r="C198" s="96"/>
+      <c r="G197" s="50"/>
+    </row>
+    <row r="198" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A198" s="83"/>
+      <c r="B198" s="89"/>
+      <c r="C198" s="86"/>
       <c r="D198" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E198" s="22" t="s">
+      <c r="E198" s="20" t="s">
         <v>331</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>681</v>
       </c>
-      <c r="G198" s="55"/>
-    </row>
-    <row r="199" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A199" s="88"/>
-      <c r="B199" s="99"/>
-      <c r="C199" s="96"/>
+      <c r="G198" s="50"/>
+    </row>
+    <row r="199" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A199" s="83"/>
+      <c r="B199" s="89"/>
+      <c r="C199" s="86"/>
       <c r="D199" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E199" s="22" t="s">
+      <c r="E199" s="20" t="s">
         <v>331</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="G199" s="55"/>
-    </row>
-    <row r="200" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A200" s="89"/>
-      <c r="B200" s="99"/>
-      <c r="C200" s="96"/>
+      <c r="G199" s="50"/>
+    </row>
+    <row r="200" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A200" s="84"/>
+      <c r="B200" s="89"/>
+      <c r="C200" s="86"/>
       <c r="D200" s="4" t="s">
         <v>738</v>
       </c>
-      <c r="E200" s="22" t="s">
+      <c r="E200" s="20" t="s">
         <v>331</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="G200" s="55"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A201" s="77"/>
-      <c r="B201" s="100"/>
-      <c r="C201" s="97"/>
+      <c r="G200" s="50"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="71"/>
+      <c r="B201" s="90"/>
+      <c r="C201" s="87"/>
       <c r="D201" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="E201" s="22"/>
+      <c r="E201" s="20"/>
       <c r="F201" s="1"/>
-      <c r="G201" s="55"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A202" s="54">
+      <c r="G201" s="50"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202" s="49">
         <v>50</v>
       </c>
-      <c r="B202" s="9" t="s">
+      <c r="B202" s="5" t="s">
         <v>49</v>
       </c>
       <c r="C202" s="4" t="s">
         <v>164</v>
       </c>
       <c r="D202" s="4"/>
-      <c r="E202" s="30"/>
+      <c r="E202" s="25"/>
       <c r="F202" s="6"/>
-      <c r="G202" s="55"/>
-    </row>
-    <row r="203" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A203" s="87">
+      <c r="G202" s="50"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203" s="82">
         <v>51</v>
       </c>
-      <c r="B203" s="98" t="s">
+      <c r="B203" s="88" t="s">
         <v>50</v>
       </c>
-      <c r="C203" s="95" t="s">
+      <c r="C203" s="85" t="s">
         <v>324</v>
       </c>
       <c r="D203" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="E203" s="22" t="s">
+      <c r="E203" s="20" t="s">
         <v>329</v>
       </c>
-      <c r="F203" s="19" t="s">
+      <c r="F203" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G203" s="90" t="s">
+      <c r="G203" s="108" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A204" s="88"/>
-      <c r="B204" s="99"/>
-      <c r="C204" s="96"/>
+    <row r="204" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A204" s="83"/>
+      <c r="B204" s="89"/>
+      <c r="C204" s="86"/>
       <c r="D204" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="E204" s="22" t="s">
+      <c r="E204" s="20" t="s">
         <v>326</v>
       </c>
-      <c r="F204" s="19" t="s">
+      <c r="F204" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G204" s="91"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A205" s="88"/>
-      <c r="B205" s="99"/>
-      <c r="C205" s="96"/>
+      <c r="G204" s="109"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="83"/>
+      <c r="B205" s="89"/>
+      <c r="C205" s="86"/>
       <c r="D205" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="E205" s="22" t="s">
+      <c r="E205" s="20" t="s">
         <v>325</v>
       </c>
-      <c r="F205" s="19" t="s">
+      <c r="F205" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G205" s="91"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A206" s="88"/>
-      <c r="B206" s="99"/>
-      <c r="C206" s="96"/>
+      <c r="G205" s="109"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="83"/>
+      <c r="B206" s="89"/>
+      <c r="C206" s="86"/>
       <c r="D206" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="E206" s="22" t="s">
+      <c r="E206" s="20" t="s">
         <v>327</v>
       </c>
-      <c r="F206" s="19" t="s">
+      <c r="F206" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G206" s="91"/>
-    </row>
-    <row r="207" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A207" s="88"/>
-      <c r="B207" s="99"/>
-      <c r="C207" s="96"/>
+      <c r="G206" s="109"/>
+    </row>
+    <row r="207" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A207" s="83"/>
+      <c r="B207" s="89"/>
+      <c r="C207" s="86"/>
       <c r="D207" s="4" t="s">
         <v>320</v>
       </c>
-      <c r="E207" s="22" t="s">
+      <c r="E207" s="20" t="s">
         <v>328</v>
       </c>
-      <c r="F207" s="19" t="s">
+      <c r="F207" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G207" s="91"/>
-    </row>
-    <row r="208" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A208" s="88"/>
-      <c r="B208" s="99"/>
-      <c r="C208" s="96"/>
+      <c r="G207" s="109"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="83"/>
+      <c r="B208" s="89"/>
+      <c r="C208" s="86"/>
       <c r="D208" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E208" s="22" t="s">
+      <c r="E208" s="20" t="s">
         <v>330</v>
       </c>
-      <c r="F208" s="19" t="s">
+      <c r="F208" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G208" s="91"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A209" s="88"/>
-      <c r="B209" s="99"/>
-      <c r="C209" s="96"/>
+      <c r="G208" s="109"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="83"/>
+      <c r="B209" s="89"/>
+      <c r="C209" s="86"/>
       <c r="D209" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="E209" s="22" t="s">
+      <c r="E209" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="F209" s="19" t="s">
+      <c r="F209" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G209" s="91"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A210" s="88"/>
-      <c r="B210" s="99"/>
-      <c r="C210" s="96"/>
+      <c r="G209" s="109"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210" s="83"/>
+      <c r="B210" s="89"/>
+      <c r="C210" s="86"/>
       <c r="D210" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="E210" s="22" t="s">
+      <c r="E210" s="20" t="s">
         <v>331</v>
       </c>
-      <c r="F210" s="19" t="s">
+      <c r="F210" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G210" s="91"/>
-    </row>
-    <row r="211" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A211" s="89"/>
-      <c r="B211" s="100"/>
-      <c r="C211" s="97"/>
+      <c r="G210" s="109"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" s="84"/>
+      <c r="B211" s="90"/>
+      <c r="C211" s="87"/>
       <c r="D211" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="E211" s="22" t="s">
+      <c r="E211" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="F211" s="19" t="s">
+      <c r="F211" s="18" t="s">
         <v>715</v>
       </c>
-      <c r="G211" s="92"/>
-    </row>
-    <row r="212" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A212" s="54">
+      <c r="G211" s="110"/>
+    </row>
+    <row r="212" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A212" s="49">
         <v>52</v>
       </c>
-      <c r="B212" s="9" t="s">
+      <c r="B212" s="5" t="s">
         <v>51</v>
       </c>
       <c r="C212" s="4" t="s">
         <v>288</v>
       </c>
       <c r="D212" s="4"/>
-      <c r="E212" s="30"/>
+      <c r="E212" s="25"/>
       <c r="F212" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="G212" s="55"/>
-    </row>
-    <row r="213" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A213" s="54">
+      <c r="G212" s="50"/>
+    </row>
+    <row r="213" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A213" s="49">
         <v>53</v>
       </c>
-      <c r="B213" s="9" t="s">
+      <c r="B213" s="5" t="s">
         <v>52</v>
       </c>
       <c r="C213" s="4" t="s">
         <v>289</v>
       </c>
       <c r="D213" s="4"/>
-      <c r="E213" s="30"/>
+      <c r="E213" s="25"/>
       <c r="F213" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="G213" s="55"/>
-    </row>
-    <row r="214" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A214" s="54">
+      <c r="G213" s="50"/>
+    </row>
+    <row r="214" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A214" s="49">
         <v>54</v>
       </c>
-      <c r="B214" s="9" t="s">
+      <c r="B214" s="5" t="s">
         <v>53</v>
       </c>
       <c r="C214" s="4" t="s">
         <v>165</v>
       </c>
       <c r="D214" s="4"/>
-      <c r="E214" s="30"/>
-      <c r="F214" s="18" t="s">
+      <c r="E214" s="25"/>
+      <c r="F214" s="17" t="s">
         <v>694</v>
       </c>
-      <c r="G214" s="55"/>
-    </row>
-    <row r="215" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A215" s="54">
+      <c r="G214" s="50"/>
+    </row>
+    <row r="215" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A215" s="49">
         <v>55</v>
       </c>
-      <c r="B215" s="9" t="s">
+      <c r="B215" s="5" t="s">
         <v>54</v>
       </c>
       <c r="C215" s="4" t="s">
         <v>166</v>
       </c>
       <c r="D215" s="4"/>
-      <c r="E215" s="30"/>
+      <c r="E215" s="25"/>
       <c r="F215" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G215" s="55"/>
-    </row>
-    <row r="216" spans="1:7" ht="165" x14ac:dyDescent="0.25">
-      <c r="A216" s="54">
+      <c r="G215" s="50"/>
+    </row>
+    <row r="216" spans="1:7" ht="145" x14ac:dyDescent="0.35">
+      <c r="A216" s="49">
         <v>56</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C216" s="28" t="s">
+      <c r="C216" s="4" t="s">
         <v>167</v>
       </c>
       <c r="D216" s="4"/>
-      <c r="E216" s="30"/>
+      <c r="E216" s="25"/>
       <c r="F216" s="6" t="s">
         <v>604</v>
       </c>
-      <c r="G216" s="55"/>
-    </row>
-    <row r="217" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A217" s="54">
+      <c r="G216" s="50"/>
+    </row>
+    <row r="217" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A217" s="49">
         <v>57</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C217" s="29" t="s">
+      <c r="C217" s="2" t="s">
         <v>168</v>
       </c>
       <c r="D217" s="4"/>
-      <c r="E217" s="30"/>
+      <c r="E217" s="25"/>
       <c r="F217" s="6" t="s">
         <v>606</v>
       </c>
-      <c r="G217" s="55"/>
-    </row>
-    <row r="218" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A218" s="54">
+      <c r="G217" s="50"/>
+    </row>
+    <row r="218" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A218" s="49">
         <v>58</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C218" s="28" t="s">
+      <c r="C218" s="4" t="s">
         <v>169</v>
       </c>
       <c r="D218" s="4"/>
-      <c r="E218" s="22" t="s">
+      <c r="E218" s="20" t="s">
         <v>635</v>
       </c>
       <c r="F218" s="6" t="s">
         <v>605</v>
       </c>
-      <c r="G218" s="55"/>
-    </row>
-    <row r="219" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A219" s="54">
+      <c r="G218" s="50"/>
+    </row>
+    <row r="219" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A219" s="49">
         <v>59</v>
       </c>
-      <c r="B219" s="9" t="s">
+      <c r="B219" s="5" t="s">
         <v>58</v>
       </c>
       <c r="C219" s="4" t="s">
         <v>170</v>
       </c>
       <c r="D219" s="4"/>
-      <c r="E219" s="30"/>
+      <c r="E219" s="25"/>
       <c r="F219" s="1" t="s">
         <v>696</v>
       </c>
-      <c r="G219" s="55"/>
-    </row>
-    <row r="220" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="54">
+      <c r="G219" s="50"/>
+    </row>
+    <row r="220" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A220" s="49">
         <v>60</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C220" s="28" t="s">
+      <c r="C220" s="4" t="s">
         <v>171</v>
       </c>
       <c r="D220" s="4"/>
-      <c r="E220" s="30"/>
+      <c r="E220" s="25"/>
       <c r="F220" s="6" t="s">
         <v>617</v>
       </c>
-      <c r="G220" s="55"/>
-    </row>
-    <row r="221" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A221" s="54">
+      <c r="G220" s="50"/>
+    </row>
+    <row r="221" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A221" s="49">
         <v>61</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C221" s="28" t="s">
+      <c r="C221" s="4" t="s">
         <v>616</v>
       </c>
       <c r="D221" s="4"/>
-      <c r="E221" s="30"/>
-      <c r="F221" s="18" t="s">
+      <c r="E221" s="25"/>
+      <c r="F221" s="17" t="s">
         <v>697</v>
       </c>
-      <c r="G221" s="55"/>
-    </row>
-    <row r="222" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A222" s="54">
+      <c r="G221" s="50"/>
+    </row>
+    <row r="222" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A222" s="49">
         <v>62</v>
       </c>
-      <c r="B222" s="9" t="s">
+      <c r="B222" s="5" t="s">
         <v>61</v>
       </c>
       <c r="C222" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D222" s="4"/>
-      <c r="E222" s="30"/>
+      <c r="E222" s="25"/>
       <c r="F222" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="G222" s="55"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A223" s="54">
+      <c r="G222" s="50"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="49">
         <v>63</v>
       </c>
-      <c r="B223" s="9" t="s">
+      <c r="B223" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C223" s="4" t="s">
         <v>229</v>
       </c>
       <c r="D223" s="4"/>
-      <c r="E223" s="30"/>
+      <c r="E223" s="25"/>
       <c r="F223" s="6"/>
-      <c r="G223" s="55"/>
-    </row>
-    <row r="224" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A224" s="54">
+      <c r="G223" s="50"/>
+    </row>
+    <row r="224" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A224" s="49">
         <v>64</v>
       </c>
-      <c r="B224" s="9" t="s">
+      <c r="B224" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C224" s="4" t="s">
         <v>172</v>
       </c>
       <c r="D224" s="4"/>
-      <c r="E224" s="30"/>
-      <c r="F224" s="18" t="s">
+      <c r="E224" s="25"/>
+      <c r="F224" s="17" t="s">
         <v>699</v>
       </c>
-      <c r="G224" s="55"/>
-    </row>
-    <row r="225" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A225" s="54">
+      <c r="G224" s="50"/>
+    </row>
+    <row r="225" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A225" s="49">
         <v>65</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C225" s="28" t="s">
+      <c r="C225" s="4" t="s">
         <v>173</v>
       </c>
       <c r="D225" s="4"/>
-      <c r="E225" s="30"/>
+      <c r="E225" s="25"/>
       <c r="F225" s="6" t="s">
         <v>607</v>
       </c>
-      <c r="G225" s="55"/>
-    </row>
-    <row r="226" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A226" s="54">
+      <c r="G225" s="50"/>
+    </row>
+    <row r="226" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A226" s="49">
         <v>66</v>
       </c>
-      <c r="B226" s="9" t="s">
+      <c r="B226" s="5" t="s">
         <v>65</v>
       </c>
       <c r="C226" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D226" s="4"/>
-      <c r="E226" s="30"/>
-      <c r="F226" s="18" t="s">
+      <c r="E226" s="25"/>
+      <c r="F226" s="17" t="s">
         <v>700</v>
       </c>
-      <c r="G226" s="55"/>
-    </row>
-    <row r="227" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A227" s="54">
+      <c r="G226" s="50"/>
+    </row>
+    <row r="227" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A227" s="49">
         <v>67</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C227" s="29" t="s">
+      <c r="C227" s="2" t="s">
         <v>230</v>
       </c>
       <c r="D227" s="4"/>
-      <c r="E227" s="30"/>
+      <c r="E227" s="25"/>
       <c r="F227" s="6" t="s">
         <v>630</v>
       </c>
-      <c r="G227" s="55"/>
-    </row>
-    <row r="228" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="122">
+      <c r="G227" s="50"/>
+    </row>
+    <row r="228" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A228" s="93">
         <v>68</v>
       </c>
-      <c r="B228" s="120" t="s">
+      <c r="B228" s="91" t="s">
         <v>67</v>
       </c>
-      <c r="C228" s="95" t="s">
+      <c r="C228" s="85" t="s">
         <v>357</v>
       </c>
       <c r="D228" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="E228" s="30" t="s">
+      <c r="E228" s="25" t="s">
         <v>307</v>
       </c>
-      <c r="F228" s="94" t="s">
+      <c r="F228" s="112" t="s">
         <v>714</v>
       </c>
-      <c r="G228" s="55"/>
-    </row>
-    <row r="229" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="123"/>
-      <c r="B229" s="121"/>
-      <c r="C229" s="97"/>
+      <c r="G228" s="50"/>
+    </row>
+    <row r="229" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A229" s="94"/>
+      <c r="B229" s="92"/>
+      <c r="C229" s="87"/>
       <c r="D229" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="E229" s="30" t="s">
+      <c r="E229" s="25" t="s">
         <v>308</v>
       </c>
-      <c r="F229" s="94"/>
-      <c r="G229" s="55"/>
-    </row>
-    <row r="230" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A230" s="87">
+      <c r="F229" s="112"/>
+      <c r="G229" s="50"/>
+    </row>
+    <row r="230" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A230" s="82">
         <v>69</v>
       </c>
-      <c r="B230" s="98" t="s">
+      <c r="B230" s="88" t="s">
         <v>68</v>
       </c>
-      <c r="C230" s="95" t="s">
+      <c r="C230" s="85" t="s">
         <v>361</v>
       </c>
       <c r="D230" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="E230" s="30" t="s">
+      <c r="E230" s="25" t="s">
         <v>358</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="G230" s="55"/>
-    </row>
-    <row r="231" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A231" s="88"/>
-      <c r="B231" s="99"/>
-      <c r="C231" s="96"/>
+      <c r="G230" s="50"/>
+    </row>
+    <row r="231" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A231" s="83"/>
+      <c r="B231" s="89"/>
+      <c r="C231" s="86"/>
       <c r="D231" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="E231" s="30" t="s">
+      <c r="E231" s="25" t="s">
         <v>359</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="G231" s="55"/>
-    </row>
-    <row r="232" spans="1:7" ht="390" x14ac:dyDescent="0.25">
-      <c r="A232" s="88"/>
-      <c r="B232" s="99"/>
-      <c r="C232" s="96"/>
+      <c r="G231" s="50"/>
+    </row>
+    <row r="232" spans="1:7" ht="348" x14ac:dyDescent="0.35">
+      <c r="A232" s="83"/>
+      <c r="B232" s="89"/>
+      <c r="C232" s="86"/>
       <c r="D232" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="E232" s="30" t="s">
+      <c r="E232" s="25" t="s">
         <v>719</v>
       </c>
-      <c r="F232" s="18" t="s">
+      <c r="F232" s="17" t="s">
         <v>720</v>
       </c>
-      <c r="G232" s="55"/>
-    </row>
-    <row r="233" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A233" s="88"/>
-      <c r="B233" s="99"/>
-      <c r="C233" s="96"/>
+      <c r="G232" s="50"/>
+    </row>
+    <row r="233" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A233" s="83"/>
+      <c r="B233" s="89"/>
+      <c r="C233" s="86"/>
       <c r="D233" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="E233" s="30" t="s">
+      <c r="E233" s="25" t="s">
         <v>360</v>
       </c>
       <c r="F233" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="G233" s="55"/>
-    </row>
-    <row r="234" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A234" s="88"/>
-      <c r="B234" s="99"/>
-      <c r="C234" s="96"/>
+      <c r="G233" s="50"/>
+    </row>
+    <row r="234" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A234" s="83"/>
+      <c r="B234" s="89"/>
+      <c r="C234" s="86"/>
       <c r="D234" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E234" s="40" t="s">
+      <c r="E234" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="F234" s="18" t="s">
+      <c r="F234" s="17" t="s">
         <v>722</v>
       </c>
-      <c r="G234" s="55"/>
-    </row>
-    <row r="235" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A235" s="88"/>
-      <c r="B235" s="99"/>
-      <c r="C235" s="96"/>
+      <c r="G234" s="50"/>
+    </row>
+    <row r="235" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A235" s="83"/>
+      <c r="B235" s="89"/>
+      <c r="C235" s="86"/>
       <c r="D235" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="E235" s="30" t="s">
+      <c r="E235" s="25" t="s">
         <v>356</v>
       </c>
-      <c r="F235" s="18" t="s">
+      <c r="F235" s="17" t="s">
         <v>723</v>
       </c>
-      <c r="G235" s="55"/>
-    </row>
-    <row r="236" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A236" s="88"/>
-      <c r="B236" s="99"/>
-      <c r="C236" s="96"/>
+      <c r="G235" s="50"/>
+    </row>
+    <row r="236" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A236" s="83"/>
+      <c r="B236" s="89"/>
+      <c r="C236" s="86"/>
       <c r="D236" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="E236" s="30" t="s">
+      <c r="E236" s="25" t="s">
         <v>746</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G236" s="55"/>
-    </row>
-    <row r="237" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A237" s="88"/>
-      <c r="B237" s="99"/>
-      <c r="C237" s="96"/>
+      <c r="G236" s="50"/>
+    </row>
+    <row r="237" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A237" s="83"/>
+      <c r="B237" s="89"/>
+      <c r="C237" s="86"/>
       <c r="D237" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="E237" s="30" t="s">
+      <c r="E237" s="25" t="s">
         <v>790</v>
       </c>
-      <c r="F237" s="18" t="s">
+      <c r="F237" s="17" t="s">
         <v>793</v>
       </c>
-      <c r="G237" s="55"/>
-    </row>
-    <row r="238" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A238" s="88"/>
-      <c r="B238" s="99"/>
-      <c r="C238" s="96"/>
+      <c r="G237" s="50"/>
+    </row>
+    <row r="238" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A238" s="83"/>
+      <c r="B238" s="89"/>
+      <c r="C238" s="86"/>
       <c r="D238" s="4" t="s">
         <v>750</v>
       </c>
-      <c r="E238" s="30" t="s">
+      <c r="E238" s="25" t="s">
         <v>789</v>
       </c>
-      <c r="F238" s="18" t="s">
+      <c r="F238" s="17" t="s">
         <v>794</v>
       </c>
-      <c r="G238" s="55"/>
-    </row>
-    <row r="239" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A239" s="88"/>
-      <c r="B239" s="99"/>
-      <c r="C239" s="96"/>
+      <c r="G238" s="50"/>
+    </row>
+    <row r="239" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A239" s="83"/>
+      <c r="B239" s="89"/>
+      <c r="C239" s="86"/>
       <c r="D239" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="E239" s="30" t="s">
+      <c r="E239" s="25" t="s">
         <v>791</v>
       </c>
       <c r="F239" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="G239" s="55"/>
-    </row>
-    <row r="240" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A240" s="88"/>
-      <c r="B240" s="99"/>
-      <c r="C240" s="96"/>
+      <c r="G239" s="50"/>
+    </row>
+    <row r="240" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A240" s="83"/>
+      <c r="B240" s="89"/>
+      <c r="C240" s="86"/>
       <c r="D240" s="4" t="s">
         <v>748</v>
       </c>
-      <c r="E240" s="30" t="s">
+      <c r="E240" s="25" t="s">
         <v>748</v>
       </c>
-      <c r="F240" s="18" t="s">
+      <c r="F240" s="17" t="s">
         <v>796</v>
       </c>
-      <c r="G240" s="55"/>
-    </row>
-    <row r="241" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A241" s="88"/>
-      <c r="B241" s="99"/>
-      <c r="C241" s="96"/>
+      <c r="G240" s="50"/>
+    </row>
+    <row r="241" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A241" s="83"/>
+      <c r="B241" s="89"/>
+      <c r="C241" s="86"/>
       <c r="D241" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="E241" s="30" t="s">
+      <c r="E241" s="25" t="s">
         <v>792</v>
       </c>
-      <c r="F241" s="18" t="s">
+      <c r="F241" s="17" t="s">
         <v>797</v>
       </c>
-      <c r="G241" s="55"/>
-    </row>
-    <row r="242" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A242" s="88"/>
-      <c r="B242" s="99"/>
-      <c r="C242" s="96"/>
+      <c r="G241" s="50"/>
+    </row>
+    <row r="242" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A242" s="83"/>
+      <c r="B242" s="89"/>
+      <c r="C242" s="86"/>
       <c r="D242" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="E242" s="30" t="s">
+      <c r="E242" s="25" t="s">
         <v>788</v>
       </c>
-      <c r="F242" s="18" t="s">
+      <c r="F242" s="17" t="s">
         <v>798</v>
       </c>
-      <c r="G242" s="55"/>
-    </row>
-    <row r="243" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A243" s="89"/>
-      <c r="B243" s="100"/>
-      <c r="C243" s="97"/>
+      <c r="G242" s="50"/>
+    </row>
+    <row r="243" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A243" s="84"/>
+      <c r="B243" s="90"/>
+      <c r="C243" s="87"/>
       <c r="D243" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="E243" s="30" t="s">
+      <c r="E243" s="25" t="s">
         <v>787</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="G243" s="55"/>
-    </row>
-    <row r="244" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A244" s="54">
+      <c r="G243" s="50"/>
+    </row>
+    <row r="244" spans="1:7" ht="116" x14ac:dyDescent="0.35">
+      <c r="A244" s="49">
         <v>70</v>
       </c>
-      <c r="B244" s="9" t="s">
+      <c r="B244" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C244" s="4" t="s">
         <v>175</v>
       </c>
       <c r="D244" s="8"/>
-      <c r="E244" s="41"/>
+      <c r="E244" s="36"/>
       <c r="F244" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="G244" s="55"/>
-    </row>
-    <row r="245" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A245" s="54">
+      <c r="G244" s="50"/>
+    </row>
+    <row r="245" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A245" s="49">
         <v>71</v>
       </c>
-      <c r="B245" s="9" t="s">
+      <c r="B245" s="5" t="s">
         <v>70</v>
       </c>
       <c r="C245" s="4" t="s">
         <v>176</v>
       </c>
       <c r="D245" s="4"/>
-      <c r="E245" s="30"/>
+      <c r="E245" s="25"/>
       <c r="F245" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="G245" s="55"/>
-    </row>
-    <row r="246" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A246" s="54">
+      <c r="G245" s="50"/>
+    </row>
+    <row r="246" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A246" s="49">
         <v>72</v>
       </c>
-      <c r="B246" s="9" t="s">
+      <c r="B246" s="5" t="s">
         <v>71</v>
       </c>
       <c r="C246" s="4" t="s">
         <v>177</v>
       </c>
       <c r="D246" s="4"/>
-      <c r="E246" s="30"/>
+      <c r="E246" s="25"/>
       <c r="F246" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="G246" s="55"/>
-    </row>
-    <row r="247" spans="1:7" ht="255" x14ac:dyDescent="0.25">
-      <c r="A247" s="54">
+      <c r="G246" s="50"/>
+    </row>
+    <row r="247" spans="1:7" ht="203" x14ac:dyDescent="0.35">
+      <c r="A247" s="49">
         <v>73</v>
       </c>
-      <c r="B247" s="9" t="s">
+      <c r="B247" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C247" s="4" t="s">
         <v>178</v>
       </c>
       <c r="D247" s="4"/>
-      <c r="E247" s="30"/>
+      <c r="E247" s="25"/>
       <c r="F247" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="G247" s="55"/>
-    </row>
-    <row r="248" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="54">
+      <c r="G247" s="50"/>
+    </row>
+    <row r="248" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A248" s="49">
         <v>74</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C248" s="28" t="s">
+      <c r="C248" s="4" t="s">
         <v>179</v>
       </c>
       <c r="D248" s="4"/>
-      <c r="E248" s="30"/>
+      <c r="E248" s="25"/>
       <c r="F248" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G248" s="55"/>
-    </row>
-    <row r="249" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="54">
+      <c r="G248" s="50"/>
+    </row>
+    <row r="249" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A249" s="49">
         <v>75</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C249" s="28" t="s">
+      <c r="C249" s="4" t="s">
         <v>232</v>
       </c>
       <c r="D249" s="4"/>
-      <c r="E249" s="30"/>
+      <c r="E249" s="25"/>
       <c r="F249" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="G249" s="55"/>
-    </row>
-    <row r="250" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A250" s="54">
+      <c r="G249" s="50"/>
+    </row>
+    <row r="250" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A250" s="49">
         <v>76</v>
       </c>
-      <c r="B250" s="9" t="s">
+      <c r="B250" s="5" t="s">
         <v>75</v>
       </c>
       <c r="C250" s="4" t="s">
         <v>180</v>
       </c>
       <c r="D250" s="4"/>
-      <c r="E250" s="30"/>
+      <c r="E250" s="25"/>
       <c r="F250" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="G250" s="55"/>
-    </row>
-    <row r="251" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A251" s="54">
+      <c r="G250" s="50"/>
+    </row>
+    <row r="251" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A251" s="49">
         <v>77</v>
       </c>
-      <c r="B251" s="9" t="s">
+      <c r="B251" s="5" t="s">
         <v>76</v>
       </c>
       <c r="C251" s="4" t="s">
         <v>181</v>
       </c>
       <c r="D251" s="4"/>
-      <c r="E251" s="30"/>
-      <c r="F251" s="18" t="s">
+      <c r="E251" s="25"/>
+      <c r="F251" s="17" t="s">
         <v>762</v>
       </c>
-      <c r="G251" s="55"/>
-    </row>
-    <row r="252" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A252" s="54">
+      <c r="G251" s="50"/>
+    </row>
+    <row r="252" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A252" s="49">
         <v>78</v>
       </c>
-      <c r="B252" s="9" t="s">
+      <c r="B252" s="5" t="s">
         <v>77</v>
       </c>
       <c r="C252" s="4" t="s">
         <v>182</v>
       </c>
       <c r="D252" s="4"/>
-      <c r="E252" s="30"/>
+      <c r="E252" s="25"/>
       <c r="F252" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="G252" s="55"/>
-    </row>
-    <row r="253" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A253" s="54">
+      <c r="G252" s="50"/>
+    </row>
+    <row r="253" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A253" s="49">
         <v>79</v>
       </c>
-      <c r="B253" s="9" t="s">
+      <c r="B253" s="5" t="s">
         <v>78</v>
       </c>
       <c r="C253" s="4" t="s">
         <v>183</v>
       </c>
       <c r="D253" s="4"/>
-      <c r="E253" s="30"/>
-      <c r="F253" s="18" t="s">
+      <c r="E253" s="25"/>
+      <c r="F253" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="G253" s="55"/>
-    </row>
-    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A254" s="54">
+      <c r="G253" s="50"/>
+    </row>
+    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A254" s="49">
         <v>80</v>
       </c>
-      <c r="B254" s="9" t="s">
+      <c r="B254" s="5" t="s">
         <v>79</v>
       </c>
       <c r="C254" s="4" t="s">
         <v>184</v>
       </c>
       <c r="D254" s="4"/>
-      <c r="E254" s="30"/>
-      <c r="F254" s="18" t="s">
+      <c r="E254" s="25"/>
+      <c r="F254" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="G254" s="55"/>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A255" s="87">
+      <c r="G254" s="50"/>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A255" s="82">
         <v>81</v>
       </c>
-      <c r="B255" s="98" t="s">
+      <c r="B255" s="88" t="s">
         <v>80</v>
       </c>
-      <c r="C255" s="120" t="s">
+      <c r="C255" s="91" t="s">
         <v>185</v>
       </c>
       <c r="D255" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E255" s="30" t="s">
+      <c r="E255" s="25" t="s">
         <v>602</v>
       </c>
       <c r="F255" s="6" t="s">
         <v>602</v>
       </c>
-      <c r="G255" s="90" t="s">
+      <c r="G255" s="108" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A256" s="88"/>
-      <c r="B256" s="99"/>
-      <c r="C256" s="124"/>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A256" s="83"/>
+      <c r="B256" s="89"/>
+      <c r="C256" s="95"/>
       <c r="D256" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E256" s="30" t="s">
+      <c r="E256" s="25" t="s">
         <v>411</v>
       </c>
       <c r="F256" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="G256" s="91"/>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A257" s="88"/>
-      <c r="B257" s="99"/>
-      <c r="C257" s="124"/>
+      <c r="G256" s="109"/>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A257" s="83"/>
+      <c r="B257" s="89"/>
+      <c r="C257" s="95"/>
       <c r="D257" s="4" t="s">
         <v>396</v>
       </c>
-      <c r="E257" s="30" t="s">
+      <c r="E257" s="25" t="s">
         <v>412</v>
       </c>
       <c r="F257" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="G257" s="91"/>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A258" s="88"/>
-      <c r="B258" s="99"/>
-      <c r="C258" s="124"/>
+      <c r="G257" s="109"/>
+    </row>
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A258" s="83"/>
+      <c r="B258" s="89"/>
+      <c r="C258" s="95"/>
       <c r="D258" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="E258" s="30" t="s">
+      <c r="E258" s="25" t="s">
         <v>625</v>
       </c>
       <c r="F258" s="6" t="s">
         <v>625</v>
       </c>
-      <c r="G258" s="91"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A259" s="88"/>
-      <c r="B259" s="99"/>
-      <c r="C259" s="124"/>
+      <c r="G258" s="109"/>
+    </row>
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A259" s="83"/>
+      <c r="B259" s="89"/>
+      <c r="C259" s="95"/>
       <c r="D259" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="E259" s="30" t="s">
+      <c r="E259" s="25" t="s">
         <v>603</v>
       </c>
       <c r="F259" s="6" t="s">
         <v>603</v>
       </c>
-      <c r="G259" s="91"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A260" s="88"/>
-      <c r="B260" s="99"/>
-      <c r="C260" s="124"/>
+      <c r="G259" s="109"/>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A260" s="83"/>
+      <c r="B260" s="89"/>
+      <c r="C260" s="95"/>
       <c r="D260" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="E260" s="30" t="s">
+      <c r="E260" s="25" t="s">
         <v>614</v>
       </c>
       <c r="F260" s="6" t="s">
         <v>614</v>
       </c>
-      <c r="G260" s="91"/>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A261" s="88"/>
-      <c r="B261" s="99"/>
-      <c r="C261" s="124"/>
+      <c r="G260" s="109"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A261" s="83"/>
+      <c r="B261" s="89"/>
+      <c r="C261" s="95"/>
       <c r="D261" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="E261" s="22" t="s">
+      <c r="E261" s="20" t="s">
         <v>626</v>
       </c>
       <c r="F261" s="6" t="s">
         <v>626</v>
       </c>
-      <c r="G261" s="91"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A262" s="88"/>
-      <c r="B262" s="99"/>
-      <c r="C262" s="124"/>
+      <c r="G261" s="109"/>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A262" s="83"/>
+      <c r="B262" s="89"/>
+      <c r="C262" s="95"/>
       <c r="D262" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E262" s="30" t="s">
+      <c r="E262" s="25" t="s">
         <v>615</v>
       </c>
       <c r="F262" s="6" t="s">
         <v>615</v>
       </c>
-      <c r="G262" s="91"/>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A263" s="88"/>
-      <c r="B263" s="99"/>
-      <c r="C263" s="124"/>
+      <c r="G262" s="109"/>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A263" s="83"/>
+      <c r="B263" s="89"/>
+      <c r="C263" s="95"/>
       <c r="D263" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="E263" s="30" t="s">
+      <c r="E263" s="25" t="s">
         <v>413</v>
       </c>
       <c r="F263" s="6" t="s">
         <v>413</v>
       </c>
-      <c r="G263" s="91"/>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A264" s="88"/>
-      <c r="B264" s="99"/>
-      <c r="C264" s="124"/>
+      <c r="G263" s="109"/>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A264" s="83"/>
+      <c r="B264" s="89"/>
+      <c r="C264" s="95"/>
       <c r="D264" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="E264" s="30" t="s">
+      <c r="E264" s="25" t="s">
         <v>620</v>
       </c>
       <c r="F264" s="6" t="s">
         <v>620</v>
       </c>
-      <c r="G264" s="91"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A265" s="88"/>
-      <c r="B265" s="99"/>
-      <c r="C265" s="124"/>
+      <c r="G264" s="109"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" s="83"/>
+      <c r="B265" s="89"/>
+      <c r="C265" s="95"/>
       <c r="D265" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="E265" s="30" t="s">
+      <c r="E265" s="25" t="s">
         <v>624</v>
       </c>
       <c r="F265" s="6" t="s">
         <v>624</v>
       </c>
-      <c r="G265" s="91"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A266" s="88"/>
-      <c r="B266" s="99"/>
-      <c r="C266" s="124"/>
+      <c r="G265" s="109"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A266" s="83"/>
+      <c r="B266" s="89"/>
+      <c r="C266" s="95"/>
       <c r="D266" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="E266" s="30" t="s">
+      <c r="E266" s="25" t="s">
         <v>623</v>
       </c>
       <c r="F266" s="6" t="s">
         <v>623</v>
       </c>
-      <c r="G266" s="91"/>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A267" s="88"/>
-      <c r="B267" s="99"/>
-      <c r="C267" s="124"/>
+      <c r="G266" s="109"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A267" s="83"/>
+      <c r="B267" s="89"/>
+      <c r="C267" s="95"/>
       <c r="D267" s="4" t="s">
         <v>400</v>
       </c>
-      <c r="E267" s="30" t="s">
+      <c r="E267" s="25" t="s">
         <v>619</v>
       </c>
       <c r="F267" s="6" t="s">
         <v>619</v>
       </c>
-      <c r="G267" s="91"/>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A268" s="88"/>
-      <c r="B268" s="99"/>
-      <c r="C268" s="124"/>
+      <c r="G267" s="109"/>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A268" s="83"/>
+      <c r="B268" s="89"/>
+      <c r="C268" s="95"/>
       <c r="D268" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="E268" s="30" t="s">
+      <c r="E268" s="25" t="s">
         <v>612</v>
       </c>
       <c r="F268" s="6" t="s">
         <v>612</v>
       </c>
-      <c r="G268" s="91"/>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A269" s="88"/>
-      <c r="B269" s="99"/>
-      <c r="C269" s="124"/>
+      <c r="G268" s="109"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="83"/>
+      <c r="B269" s="89"/>
+      <c r="C269" s="95"/>
       <c r="D269" s="4" t="s">
         <v>402</v>
       </c>
-      <c r="E269" s="30" t="s">
+      <c r="E269" s="25" t="s">
         <v>613</v>
       </c>
       <c r="F269" s="6" t="s">
         <v>613</v>
       </c>
-      <c r="G269" s="91"/>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A270" s="88"/>
-      <c r="B270" s="99"/>
-      <c r="C270" s="124"/>
+      <c r="G269" s="109"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A270" s="83"/>
+      <c r="B270" s="89"/>
+      <c r="C270" s="95"/>
       <c r="D270" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="E270" s="22" t="s">
+      <c r="E270" s="20" t="s">
         <v>627</v>
       </c>
       <c r="F270" s="6" t="s">
         <v>627</v>
       </c>
-      <c r="G270" s="91"/>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A271" s="88"/>
-      <c r="B271" s="99"/>
-      <c r="C271" s="124"/>
+      <c r="G270" s="109"/>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A271" s="83"/>
+      <c r="B271" s="89"/>
+      <c r="C271" s="95"/>
       <c r="D271" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="E271" s="30" t="s">
+      <c r="E271" s="25" t="s">
         <v>628</v>
       </c>
       <c r="F271" s="6" t="s">
         <v>628</v>
       </c>
-      <c r="G271" s="91"/>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A272" s="88"/>
-      <c r="B272" s="99"/>
-      <c r="C272" s="124"/>
+      <c r="G271" s="109"/>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A272" s="83"/>
+      <c r="B272" s="89"/>
+      <c r="C272" s="95"/>
       <c r="D272" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="E272" s="30" t="s">
+      <c r="E272" s="25" t="s">
         <v>414</v>
       </c>
       <c r="F272" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="G272" s="91"/>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A273" s="88"/>
-      <c r="B273" s="99"/>
-      <c r="C273" s="124"/>
+      <c r="G272" s="109"/>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A273" s="83"/>
+      <c r="B273" s="89"/>
+      <c r="C273" s="95"/>
       <c r="D273" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="E273" s="30" t="s">
+      <c r="E273" s="25" t="s">
         <v>410</v>
       </c>
       <c r="F273" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="G273" s="91"/>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A274" s="88"/>
-      <c r="B274" s="99"/>
-      <c r="C274" s="124"/>
+      <c r="G273" s="109"/>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A274" s="83"/>
+      <c r="B274" s="89"/>
+      <c r="C274" s="95"/>
       <c r="D274" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="E274" s="30" t="s">
+      <c r="E274" s="25" t="s">
         <v>611</v>
       </c>
       <c r="F274" s="6" t="s">
         <v>611</v>
       </c>
-      <c r="G274" s="91"/>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A275" s="88"/>
-      <c r="B275" s="99"/>
-      <c r="C275" s="124"/>
+      <c r="G274" s="109"/>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A275" s="83"/>
+      <c r="B275" s="89"/>
+      <c r="C275" s="95"/>
       <c r="D275" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="E275" s="30" t="s">
+      <c r="E275" s="25" t="s">
         <v>622</v>
       </c>
       <c r="F275" s="6" t="s">
         <v>622</v>
       </c>
-      <c r="G275" s="91"/>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A276" s="88"/>
-      <c r="B276" s="99"/>
-      <c r="C276" s="124"/>
+      <c r="G275" s="109"/>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A276" s="83"/>
+      <c r="B276" s="89"/>
+      <c r="C276" s="95"/>
       <c r="D276" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="E276" s="30" t="s">
+      <c r="E276" s="25" t="s">
         <v>415</v>
       </c>
       <c r="F276" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="G276" s="91"/>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A277" s="88"/>
-      <c r="B277" s="99"/>
-      <c r="C277" s="124"/>
+      <c r="G276" s="109"/>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A277" s="83"/>
+      <c r="B277" s="89"/>
+      <c r="C277" s="95"/>
       <c r="D277" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E277" s="30" t="s">
+      <c r="E277" s="25" t="s">
         <v>610</v>
       </c>
       <c r="F277" s="6" t="s">
         <v>610</v>
       </c>
-      <c r="G277" s="91"/>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A278" s="88"/>
-      <c r="B278" s="99"/>
-      <c r="C278" s="124"/>
+      <c r="G277" s="109"/>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" s="83"/>
+      <c r="B278" s="89"/>
+      <c r="C278" s="95"/>
       <c r="D278" s="4" t="s">
         <v>406</v>
       </c>
-      <c r="E278" s="30" t="s">
+      <c r="E278" s="25" t="s">
         <v>416</v>
       </c>
       <c r="F278" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="G278" s="91"/>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A279" s="88"/>
-      <c r="B279" s="99"/>
-      <c r="C279" s="124"/>
+      <c r="G278" s="109"/>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A279" s="83"/>
+      <c r="B279" s="89"/>
+      <c r="C279" s="95"/>
       <c r="D279" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="E279" s="30" t="s">
+      <c r="E279" s="25" t="s">
         <v>609</v>
       </c>
       <c r="F279" s="6" t="s">
         <v>609</v>
       </c>
-      <c r="G279" s="91"/>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A280" s="88"/>
-      <c r="B280" s="99"/>
-      <c r="C280" s="124"/>
+      <c r="G279" s="109"/>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A280" s="83"/>
+      <c r="B280" s="89"/>
+      <c r="C280" s="95"/>
       <c r="D280" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="E280" s="30" t="s">
+      <c r="E280" s="25" t="s">
         <v>417</v>
       </c>
       <c r="F280" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="G280" s="91"/>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A281" s="88"/>
-      <c r="B281" s="99"/>
-      <c r="C281" s="124"/>
+      <c r="G280" s="109"/>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A281" s="83"/>
+      <c r="B281" s="89"/>
+      <c r="C281" s="95"/>
       <c r="D281" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="E281" s="30" t="s">
+      <c r="E281" s="25" t="s">
         <v>621</v>
       </c>
       <c r="F281" s="6" t="s">
         <v>621</v>
       </c>
-      <c r="G281" s="91"/>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A282" s="88"/>
-      <c r="B282" s="99"/>
-      <c r="C282" s="124"/>
+      <c r="G281" s="109"/>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A282" s="83"/>
+      <c r="B282" s="89"/>
+      <c r="C282" s="95"/>
       <c r="D282" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="E282" s="30" t="s">
+      <c r="E282" s="25" t="s">
         <v>418</v>
       </c>
       <c r="F282" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="G282" s="92"/>
-    </row>
-    <row r="283" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A283" s="54">
+      <c r="G282" s="110"/>
+    </row>
+    <row r="283" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A283" s="49">
         <v>82</v>
       </c>
-      <c r="B283" s="9" t="s">
+      <c r="B283" s="5" t="s">
         <v>81</v>
       </c>
       <c r="C283" s="4" t="s">
         <v>186</v>
       </c>
       <c r="D283" s="4"/>
-      <c r="E283" s="30"/>
+      <c r="E283" s="25"/>
       <c r="F283" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G283" s="78"/>
-    </row>
-    <row r="284" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A284" s="54">
+      <c r="G283" s="72"/>
+    </row>
+    <row r="284" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A284" s="49">
         <v>83</v>
       </c>
-      <c r="B284" s="9" t="s">
+      <c r="B284" s="5" t="s">
         <v>82</v>
       </c>
       <c r="C284" s="4" t="s">
         <v>187</v>
       </c>
       <c r="D284" s="4"/>
-      <c r="E284" s="30"/>
-      <c r="F284" s="18" t="s">
+      <c r="E284" s="25"/>
+      <c r="F284" s="17" t="s">
         <v>767</v>
       </c>
-      <c r="G284" s="78"/>
-    </row>
-    <row r="285" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A285" s="54">
+      <c r="G284" s="72"/>
+    </row>
+    <row r="285" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A285" s="49">
         <v>84</v>
       </c>
-      <c r="B285" s="9" t="s">
+      <c r="B285" s="5" t="s">
         <v>83</v>
       </c>
       <c r="C285" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D285" s="4"/>
-      <c r="E285" s="30"/>
-      <c r="F285" s="18" t="s">
+      <c r="E285" s="25"/>
+      <c r="F285" s="17" t="s">
         <v>768</v>
       </c>
-      <c r="G285" s="78"/>
-    </row>
-    <row r="286" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A286" s="54">
+      <c r="G285" s="72"/>
+    </row>
+    <row r="286" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A286" s="49">
         <v>85</v>
       </c>
-      <c r="B286" s="9" t="s">
+      <c r="B286" s="5" t="s">
         <v>84</v>
       </c>
       <c r="C286" s="4" t="s">
         <v>189</v>
       </c>
       <c r="D286" s="4"/>
-      <c r="E286" s="30"/>
-      <c r="F286" s="18" t="s">
+      <c r="E286" s="25"/>
+      <c r="F286" s="17" t="s">
         <v>769</v>
       </c>
-      <c r="G286" s="78"/>
-    </row>
-    <row r="287" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A287" s="54">
+      <c r="G286" s="72"/>
+    </row>
+    <row r="287" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A287" s="49">
         <v>86</v>
       </c>
-      <c r="B287" s="9" t="s">
+      <c r="B287" s="5" t="s">
         <v>85</v>
       </c>
       <c r="C287" s="4" t="s">
         <v>190</v>
       </c>
       <c r="D287" s="4"/>
-      <c r="E287" s="30"/>
-      <c r="F287" s="18" t="s">
+      <c r="E287" s="25"/>
+      <c r="F287" s="17" t="s">
         <v>770</v>
       </c>
-      <c r="G287" s="78"/>
-    </row>
-    <row r="288" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A288" s="54">
+      <c r="G287" s="72"/>
+    </row>
+    <row r="288" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A288" s="49">
         <v>87</v>
       </c>
-      <c r="B288" s="9" t="s">
+      <c r="B288" s="5" t="s">
         <v>86</v>
       </c>
       <c r="C288" s="4" t="s">
         <v>191</v>
       </c>
       <c r="D288" s="4"/>
-      <c r="E288" s="30"/>
-      <c r="F288" s="18" t="s">
+      <c r="E288" s="25"/>
+      <c r="F288" s="17" t="s">
         <v>771</v>
       </c>
-      <c r="G288" s="78"/>
-    </row>
-    <row r="289" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A289" s="54">
+      <c r="G288" s="72"/>
+    </row>
+    <row r="289" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A289" s="49">
         <v>88</v>
       </c>
-      <c r="B289" s="9" t="s">
+      <c r="B289" s="5" t="s">
         <v>87</v>
       </c>
       <c r="C289" s="4" t="s">
         <v>192</v>
       </c>
       <c r="D289" s="4"/>
-      <c r="E289" s="30"/>
-      <c r="F289" s="18" t="s">
+      <c r="E289" s="25"/>
+      <c r="F289" s="17" t="s">
         <v>772</v>
       </c>
-      <c r="G289" s="78"/>
-    </row>
-    <row r="290" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A290" s="54">
+      <c r="G289" s="72"/>
+    </row>
+    <row r="290" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A290" s="49">
         <v>89</v>
       </c>
-      <c r="B290" s="9" t="s">
+      <c r="B290" s="5" t="s">
         <v>88</v>
       </c>
       <c r="C290" s="4" t="s">
         <v>193</v>
       </c>
       <c r="D290" s="4"/>
-      <c r="E290" s="30"/>
+      <c r="E290" s="25"/>
       <c r="F290" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G290" s="78"/>
-    </row>
-    <row r="291" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A291" s="54">
+      <c r="G290" s="72"/>
+    </row>
+    <row r="291" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A291" s="49">
         <v>90</v>
       </c>
-      <c r="B291" s="9" t="s">
+      <c r="B291" s="5" t="s">
         <v>89</v>
       </c>
       <c r="C291" s="4" t="s">
         <v>194</v>
       </c>
       <c r="D291" s="4"/>
-      <c r="E291" s="30"/>
-      <c r="F291" s="18" t="s">
+      <c r="E291" s="25"/>
+      <c r="F291" s="17" t="s">
         <v>774</v>
       </c>
-      <c r="G291" s="78"/>
-    </row>
-    <row r="292" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A292" s="54">
+      <c r="G291" s="72"/>
+    </row>
+    <row r="292" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A292" s="49">
         <v>91</v>
       </c>
-      <c r="B292" s="9" t="s">
+      <c r="B292" s="5" t="s">
         <v>90</v>
       </c>
       <c r="C292" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D292" s="4"/>
-      <c r="E292" s="30"/>
-      <c r="F292" s="18" t="s">
+      <c r="E292" s="25"/>
+      <c r="F292" s="17" t="s">
         <v>775</v>
       </c>
-      <c r="G292" s="78"/>
-    </row>
-    <row r="293" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A293" s="54">
+      <c r="G292" s="72"/>
+    </row>
+    <row r="293" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A293" s="49">
         <v>92</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="C293" s="29" t="s">
+      <c r="C293" s="2" t="s">
         <v>196</v>
       </c>
       <c r="D293" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="E293" s="30" t="s">
+      <c r="E293" s="25" t="s">
         <v>308</v>
       </c>
       <c r="F293" s="6" t="s">
         <v>608</v>
       </c>
-      <c r="G293" s="78"/>
-    </row>
-    <row r="294" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A294" s="54">
+      <c r="G293" s="72"/>
+    </row>
+    <row r="294" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A294" s="49">
         <v>93</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C294" s="28" t="s">
+      <c r="C294" s="4" t="s">
         <v>197</v>
       </c>
       <c r="D294" s="4"/>
-      <c r="E294" s="30"/>
+      <c r="E294" s="25"/>
       <c r="F294" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G294" s="78"/>
-    </row>
-    <row r="295" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A295" s="54">
+      <c r="G294" s="72"/>
+    </row>
+    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A295" s="49">
         <v>94</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C295" s="28" t="s">
+      <c r="C295" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D295" s="4"/>
-      <c r="E295" s="30"/>
+      <c r="E295" s="25"/>
       <c r="F295" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="G295" s="78"/>
-    </row>
-    <row r="296" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A296" s="54">
+      <c r="G295" s="72"/>
+    </row>
+    <row r="296" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A296" s="49">
         <v>95</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C296" s="28" t="s">
+      <c r="C296" s="4" t="s">
         <v>199</v>
       </c>
       <c r="D296" s="4"/>
-      <c r="E296" s="30"/>
+      <c r="E296" s="25"/>
       <c r="F296" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="G296" s="78"/>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A297" s="54">
+      <c r="G296" s="72"/>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A297" s="49">
         <v>96</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="C297" s="28" t="s">
+      <c r="C297" s="4" t="s">
         <v>200</v>
       </c>
       <c r="D297" s="4"/>
-      <c r="E297" s="30"/>
+      <c r="E297" s="25"/>
       <c r="F297" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G297" s="78"/>
-    </row>
-    <row r="298" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A298" s="54">
+      <c r="G297" s="72"/>
+    </row>
+    <row r="298" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A298" s="49">
         <v>97</v>
       </c>
-      <c r="B298" s="9" t="s">
+      <c r="B298" s="5" t="s">
         <v>96</v>
       </c>
       <c r="C298" s="4" t="s">
         <v>201</v>
       </c>
       <c r="D298" s="4"/>
-      <c r="E298" s="30"/>
+      <c r="E298" s="25"/>
       <c r="F298" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="G298" s="78"/>
-    </row>
-    <row r="299" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A299" s="54">
+      <c r="G298" s="72"/>
+    </row>
+    <row r="299" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A299" s="49">
         <v>98</v>
       </c>
-      <c r="B299" s="9" t="s">
+      <c r="B299" s="5" t="s">
         <v>97</v>
       </c>
       <c r="C299" s="4" t="s">
         <v>290</v>
       </c>
       <c r="D299" s="4"/>
-      <c r="E299" s="30"/>
+      <c r="E299" s="25"/>
       <c r="F299" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="G299" s="78"/>
-    </row>
-    <row r="300" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A300" s="54">
+      <c r="G299" s="72"/>
+    </row>
+    <row r="300" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A300" s="49">
         <v>99</v>
       </c>
-      <c r="B300" s="9" t="s">
+      <c r="B300" s="5" t="s">
         <v>98</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>202</v>
       </c>
       <c r="D300" s="4"/>
-      <c r="E300" s="30"/>
-      <c r="F300" s="18" t="s">
+      <c r="E300" s="25"/>
+      <c r="F300" s="17" t="s">
         <v>778</v>
       </c>
-      <c r="G300" s="78"/>
-    </row>
-    <row r="301" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A301" s="54">
+      <c r="G300" s="72"/>
+    </row>
+    <row r="301" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A301" s="49">
         <v>100</v>
       </c>
-      <c r="B301" s="9" t="s">
+      <c r="B301" s="5" t="s">
         <v>99</v>
       </c>
       <c r="C301" s="4" t="s">
         <v>203</v>
       </c>
       <c r="D301" s="4"/>
-      <c r="E301" s="30"/>
+      <c r="E301" s="25"/>
       <c r="F301" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="G301" s="78"/>
-    </row>
-    <row r="302" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A302" s="54">
+      <c r="G301" s="72"/>
+    </row>
+    <row r="302" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A302" s="49">
         <v>101</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C302" s="28" t="s">
+      <c r="C302" s="4" t="s">
         <v>204</v>
       </c>
       <c r="D302" s="4"/>
-      <c r="E302" s="30"/>
+      <c r="E302" s="25"/>
       <c r="F302" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G302" s="78"/>
-    </row>
-    <row r="303" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A303" s="54">
+      <c r="G302" s="72"/>
+    </row>
+    <row r="303" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A303" s="49">
         <v>102</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C303" s="29" t="s">
+      <c r="C303" s="2" t="s">
         <v>205</v>
       </c>
       <c r="D303" s="4"/>
-      <c r="E303" s="30"/>
+      <c r="E303" s="25"/>
       <c r="F303" s="6" t="s">
         <v>384</v>
       </c>
-      <c r="G303" s="78"/>
-    </row>
-    <row r="304" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A304" s="54">
+      <c r="G303" s="72"/>
+    </row>
+    <row r="304" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A304" s="49">
         <v>103</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C304" s="28" t="s">
+      <c r="C304" s="4" t="s">
         <v>206</v>
       </c>
       <c r="D304" s="4"/>
-      <c r="E304" s="30"/>
+      <c r="E304" s="25"/>
       <c r="F304" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="G304" s="78"/>
-    </row>
-    <row r="305" spans="1:7" ht="120" x14ac:dyDescent="0.25">
-      <c r="A305" s="54">
+      <c r="G304" s="72"/>
+    </row>
+    <row r="305" spans="1:7" ht="87" x14ac:dyDescent="0.35">
+      <c r="A305" s="49">
         <v>104</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C305" s="28" t="s">
+      <c r="C305" s="4" t="s">
         <v>207</v>
       </c>
       <c r="D305" s="4"/>
-      <c r="E305" s="30"/>
+      <c r="E305" s="25"/>
       <c r="F305" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="G305" s="78"/>
-    </row>
-    <row r="306" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A306" s="54">
+      <c r="G305" s="72"/>
+    </row>
+    <row r="306" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A306" s="49">
         <v>105</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C306" s="28" t="s">
+      <c r="C306" s="4" t="s">
         <v>208</v>
       </c>
       <c r="D306" s="4"/>
-      <c r="E306" s="30"/>
+      <c r="E306" s="25"/>
       <c r="F306" s="6" t="s">
         <v>387</v>
       </c>
-      <c r="G306" s="78"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A307" s="54">
+      <c r="G306" s="72"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A307" s="49">
         <v>106</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C307" s="28" t="s">
+      <c r="C307" s="4" t="s">
         <v>209</v>
       </c>
       <c r="D307" s="4"/>
-      <c r="E307" s="30"/>
-      <c r="F307" s="24" t="s">
+      <c r="E307" s="25"/>
+      <c r="F307" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="G307" s="78"/>
-    </row>
-    <row r="308" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A308" s="54">
+      <c r="G307" s="72"/>
+    </row>
+    <row r="308" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A308" s="49">
         <v>107</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="C308" s="28" t="s">
+      <c r="C308" s="4" t="s">
         <v>210</v>
       </c>
       <c r="D308" s="4"/>
-      <c r="E308" s="30"/>
-      <c r="F308" s="24" t="s">
+      <c r="E308" s="25"/>
+      <c r="F308" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="G308" s="78"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A309" s="54">
+      <c r="G308" s="72"/>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A309" s="49">
         <v>108</v>
       </c>
-      <c r="B309" s="14" t="s">
+      <c r="B309" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C309" s="28" t="s">
+      <c r="C309" s="4" t="s">
         <v>211</v>
       </c>
       <c r="D309" s="4"/>
-      <c r="E309" s="30"/>
+      <c r="E309" s="25"/>
       <c r="F309" s="6" t="s">
         <v>618</v>
       </c>
-      <c r="G309" s="78"/>
-    </row>
-    <row r="310" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A310" s="54">
+      <c r="G309" s="72"/>
+    </row>
+    <row r="310" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A310" s="49">
         <v>109</v>
       </c>
-      <c r="B310" s="14" t="s">
+      <c r="B310" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="C310" s="28" t="s">
+      <c r="C310" s="4" t="s">
         <v>212</v>
       </c>
       <c r="D310" s="4"/>
-      <c r="E310" s="22" t="s">
+      <c r="E310" s="20" t="s">
         <v>212</v>
       </c>
       <c r="F310" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G310" s="78"/>
-    </row>
-    <row r="311" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A311" s="54">
+      <c r="G310" s="72"/>
+    </row>
+    <row r="311" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A311" s="49">
         <v>110</v>
       </c>
-      <c r="B311" s="9" t="s">
+      <c r="B311" s="5" t="s">
         <v>108</v>
       </c>
       <c r="C311" s="4" t="s">
         <v>212</v>
       </c>
       <c r="D311" s="4"/>
-      <c r="E311" s="22" t="s">
+      <c r="E311" s="20" t="s">
         <v>212</v>
       </c>
       <c r="F311" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="G311" s="78"/>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A312" s="54">
+      <c r="G311" s="72"/>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A312" s="49">
         <v>111</v>
       </c>
-      <c r="B312" s="9" t="s">
+      <c r="B312" s="5" t="s">
         <v>109</v>
       </c>
       <c r="C312" s="4" t="s">
         <v>213</v>
       </c>
       <c r="D312" s="4"/>
-      <c r="E312" s="30"/>
+      <c r="E312" s="25"/>
       <c r="F312" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="G312" s="78"/>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A313" s="54">
+      <c r="G312" s="72"/>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A313" s="49">
         <v>112</v>
       </c>
-      <c r="B313" s="9" t="s">
+      <c r="B313" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C313" s="4" t="s">
         <v>644</v>
       </c>
       <c r="D313" s="4"/>
-      <c r="E313" s="30"/>
+      <c r="E313" s="25"/>
       <c r="F313" s="6" t="s">
         <v>644</v>
       </c>
-      <c r="G313" s="78"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A314" s="54">
+      <c r="G313" s="72"/>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314" s="49">
         <v>113</v>
       </c>
-      <c r="B314" s="9" t="s">
+      <c r="B314" s="5" t="s">
         <v>111</v>
       </c>
       <c r="C314" s="4" t="s">
         <v>214</v>
       </c>
       <c r="D314" s="4"/>
-      <c r="E314" s="30"/>
+      <c r="E314" s="25"/>
       <c r="F314" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="G314" s="78"/>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A315" s="54">
+      <c r="G314" s="72"/>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A315" s="49">
         <v>114</v>
       </c>
-      <c r="B315" s="9" t="s">
+      <c r="B315" s="5" t="s">
         <v>112</v>
       </c>
       <c r="C315" s="4" t="s">
         <v>645</v>
       </c>
       <c r="D315" s="4"/>
-      <c r="E315" s="30"/>
+      <c r="E315" s="25"/>
       <c r="F315" s="6" t="s">
         <v>645</v>
       </c>
-      <c r="G315" s="78"/>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A316" s="54">
+      <c r="G315" s="72"/>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A316" s="49">
         <v>115</v>
       </c>
-      <c r="B316" s="9" t="s">
+      <c r="B316" s="5" t="s">
         <v>113</v>
       </c>
       <c r="C316" s="4" t="s">
         <v>215</v>
       </c>
       <c r="D316" s="4"/>
-      <c r="E316" s="30"/>
+      <c r="E316" s="25"/>
       <c r="F316" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G316" s="78"/>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A317" s="54">
+      <c r="G316" s="72"/>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A317" s="49">
         <v>116</v>
       </c>
-      <c r="B317" s="9" t="s">
+      <c r="B317" s="5" t="s">
         <v>114</v>
       </c>
       <c r="C317" s="4" t="s">
         <v>216</v>
       </c>
       <c r="D317" s="4"/>
-      <c r="E317" s="30"/>
+      <c r="E317" s="25"/>
       <c r="F317" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="G317" s="78"/>
-    </row>
-    <row r="318" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A318" s="54">
+      <c r="G317" s="72"/>
+    </row>
+    <row r="318" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A318" s="49">
         <v>117</v>
       </c>
-      <c r="B318" s="9" t="s">
+      <c r="B318" s="5" t="s">
         <v>115</v>
       </c>
       <c r="C318" s="4" t="s">
         <v>217</v>
       </c>
       <c r="D318" s="4"/>
-      <c r="E318" s="30"/>
+      <c r="E318" s="25"/>
       <c r="F318" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="G318" s="78"/>
-    </row>
-    <row r="319" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A319" s="54">
+      <c r="G318" s="72"/>
+    </row>
+    <row r="319" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A319" s="49">
         <v>118</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C319" s="28" t="s">
+      <c r="C319" s="4" t="s">
         <v>218</v>
       </c>
       <c r="D319" s="4"/>
-      <c r="E319" s="30"/>
+      <c r="E319" s="25"/>
       <c r="F319" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="G319" s="78"/>
-    </row>
-    <row r="320" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A320" s="54">
+      <c r="G319" s="72"/>
+    </row>
+    <row r="320" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A320" s="49">
         <v>119</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C320" s="28" t="s">
+      <c r="C320" s="4" t="s">
         <v>219</v>
       </c>
       <c r="D320" s="4"/>
-      <c r="E320" s="30"/>
+      <c r="E320" s="25"/>
       <c r="F320" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="G320" s="78"/>
-    </row>
-    <row r="321" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A321" s="54">
+      <c r="G320" s="72"/>
+    </row>
+    <row r="321" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A321" s="49">
         <v>120</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C321" s="28" t="s">
+      <c r="C321" s="4" t="s">
         <v>220</v>
       </c>
       <c r="D321" s="4"/>
-      <c r="E321" s="30"/>
-      <c r="F321" s="18" t="s">
+      <c r="E321" s="25"/>
+      <c r="F321" s="17" t="s">
         <v>782</v>
       </c>
-      <c r="G321" s="78"/>
-    </row>
-    <row r="322" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A322" s="54">
+      <c r="G321" s="72"/>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A322" s="49">
         <v>121</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="C322" s="28" t="s">
+      <c r="C322" s="4" t="s">
         <v>221</v>
       </c>
       <c r="D322" s="4"/>
-      <c r="E322" s="30"/>
+      <c r="E322" s="25"/>
       <c r="F322" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="G322" s="78"/>
-    </row>
-    <row r="323" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A323" s="54">
+      <c r="G322" s="72"/>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A323" s="49">
         <v>122</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="C323" s="28" t="s">
+      <c r="C323" s="4" t="s">
         <v>222</v>
       </c>
       <c r="D323" s="4"/>
-      <c r="E323" s="30"/>
+      <c r="E323" s="25"/>
       <c r="F323" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="G323" s="78"/>
-    </row>
-    <row r="324" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A324" s="54">
+      <c r="G323" s="72"/>
+    </row>
+    <row r="324" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A324" s="49">
         <v>123</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="C324" s="28" t="s">
+      <c r="C324" s="4" t="s">
         <v>223</v>
       </c>
       <c r="D324" s="4"/>
-      <c r="E324" s="30"/>
+      <c r="E324" s="25"/>
       <c r="F324" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="G324" s="78"/>
-    </row>
-    <row r="325" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="87">
+      <c r="G324" s="72"/>
+    </row>
+    <row r="325" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A325" s="82">
         <v>124</v>
       </c>
-      <c r="B325" s="117" t="s">
+      <c r="B325" s="88" t="s">
         <v>122</v>
       </c>
-      <c r="C325" s="114" t="s">
+      <c r="C325" s="85" t="s">
         <v>224</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="E325" s="30" t="s">
+      <c r="E325" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="F325" s="113" t="s">
+      <c r="F325" s="81" t="s">
         <v>390</v>
       </c>
-      <c r="G325" s="78"/>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A326" s="88"/>
-      <c r="B326" s="118"/>
-      <c r="C326" s="115"/>
+      <c r="G325" s="72"/>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A326" s="83"/>
+      <c r="B326" s="89"/>
+      <c r="C326" s="86"/>
       <c r="D326" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="E326" s="30" t="s">
+      <c r="E326" s="25" t="s">
         <v>300</v>
       </c>
-      <c r="F326" s="113"/>
-      <c r="G326" s="78"/>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A327" s="88"/>
-      <c r="B327" s="118"/>
-      <c r="C327" s="115"/>
+      <c r="F326" s="81"/>
+      <c r="G326" s="72"/>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A327" s="83"/>
+      <c r="B327" s="89"/>
+      <c r="C327" s="86"/>
       <c r="D327" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="E327" s="30" t="s">
+      <c r="E327" s="25" t="s">
         <v>303</v>
       </c>
-      <c r="F327" s="113"/>
-      <c r="G327" s="78"/>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A328" s="88"/>
-      <c r="B328" s="118"/>
-      <c r="C328" s="115"/>
+      <c r="F327" s="81"/>
+      <c r="G327" s="72"/>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A328" s="83"/>
+      <c r="B328" s="89"/>
+      <c r="C328" s="86"/>
       <c r="D328" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="E328" s="30" t="s">
+      <c r="E328" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="F328" s="113"/>
-      <c r="G328" s="78"/>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A329" s="88"/>
-      <c r="B329" s="118"/>
-      <c r="C329" s="115"/>
+      <c r="F328" s="81"/>
+      <c r="G328" s="72"/>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A329" s="83"/>
+      <c r="B329" s="89"/>
+      <c r="C329" s="86"/>
       <c r="D329" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E329" s="22" t="s">
+      <c r="E329" s="20" t="s">
         <v>363</v>
       </c>
-      <c r="F329" s="113"/>
-      <c r="G329" s="78"/>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A330" s="88"/>
-      <c r="B330" s="118"/>
-      <c r="C330" s="115"/>
+      <c r="F329" s="81"/>
+      <c r="G329" s="72"/>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A330" s="83"/>
+      <c r="B330" s="89"/>
+      <c r="C330" s="86"/>
       <c r="D330" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="E330" s="30" t="s">
+      <c r="E330" s="25" t="s">
         <v>311</v>
       </c>
-      <c r="F330" s="113"/>
-      <c r="G330" s="78"/>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A331" s="88"/>
-      <c r="B331" s="118"/>
-      <c r="C331" s="115"/>
+      <c r="F330" s="81"/>
+      <c r="G330" s="72"/>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A331" s="83"/>
+      <c r="B331" s="89"/>
+      <c r="C331" s="86"/>
       <c r="D331" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E331" s="30" t="s">
+      <c r="E331" s="25" t="s">
         <v>313</v>
       </c>
-      <c r="F331" s="113"/>
-      <c r="G331" s="78"/>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A332" s="88"/>
-      <c r="B332" s="118"/>
-      <c r="C332" s="115"/>
+      <c r="F331" s="81"/>
+      <c r="G331" s="72"/>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A332" s="83"/>
+      <c r="B332" s="89"/>
+      <c r="C332" s="86"/>
       <c r="D332" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E332" s="30" t="s">
+      <c r="E332" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="F332" s="113"/>
-      <c r="G332" s="78"/>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A333" s="88"/>
-      <c r="B333" s="118"/>
-      <c r="C333" s="115"/>
+      <c r="F332" s="81"/>
+      <c r="G332" s="72"/>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A333" s="83"/>
+      <c r="B333" s="89"/>
+      <c r="C333" s="86"/>
       <c r="D333" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E333" s="30" t="s">
+      <c r="E333" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="F333" s="113"/>
-      <c r="G333" s="78"/>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A334" s="88"/>
-      <c r="B334" s="118"/>
-      <c r="C334" s="115"/>
+      <c r="F333" s="81"/>
+      <c r="G333" s="72"/>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A334" s="83"/>
+      <c r="B334" s="89"/>
+      <c r="C334" s="86"/>
       <c r="D334" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="E334" s="30" t="s">
+      <c r="E334" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="F334" s="113"/>
-      <c r="G334" s="78"/>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A335" s="88"/>
-      <c r="B335" s="118"/>
-      <c r="C335" s="115"/>
+      <c r="F334" s="81"/>
+      <c r="G334" s="72"/>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A335" s="83"/>
+      <c r="B335" s="89"/>
+      <c r="C335" s="86"/>
       <c r="D335" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="E335" s="22" t="s">
+      <c r="E335" s="20" t="s">
         <v>366</v>
       </c>
-      <c r="F335" s="113"/>
-      <c r="G335" s="78"/>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A336" s="88"/>
-      <c r="B336" s="118"/>
-      <c r="C336" s="115"/>
+      <c r="F335" s="81"/>
+      <c r="G335" s="72"/>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A336" s="83"/>
+      <c r="B336" s="89"/>
+      <c r="C336" s="86"/>
       <c r="D336" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E336" s="30" t="s">
+      <c r="E336" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="F336" s="113"/>
-      <c r="G336" s="78"/>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A337" s="88"/>
-      <c r="B337" s="118"/>
-      <c r="C337" s="115"/>
+      <c r="F336" s="81"/>
+      <c r="G336" s="72"/>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A337" s="83"/>
+      <c r="B337" s="89"/>
+      <c r="C337" s="86"/>
       <c r="D337" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="E337" s="30" t="s">
+      <c r="E337" s="25" t="s">
         <v>292</v>
       </c>
-      <c r="F337" s="113"/>
-      <c r="G337" s="78"/>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A338" s="88"/>
-      <c r="B338" s="118"/>
-      <c r="C338" s="115"/>
+      <c r="F337" s="81"/>
+      <c r="G337" s="72"/>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A338" s="83"/>
+      <c r="B338" s="89"/>
+      <c r="C338" s="86"/>
       <c r="D338" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="E338" s="30" t="s">
+      <c r="E338" s="25" t="s">
         <v>633</v>
       </c>
-      <c r="F338" s="113"/>
-      <c r="G338" s="78"/>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A339" s="88"/>
-      <c r="B339" s="118"/>
-      <c r="C339" s="115"/>
+      <c r="F338" s="81"/>
+      <c r="G338" s="72"/>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A339" s="83"/>
+      <c r="B339" s="89"/>
+      <c r="C339" s="86"/>
       <c r="D339" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="E339" s="30" t="s">
+      <c r="E339" s="25" t="s">
         <v>632</v>
       </c>
-      <c r="F339" s="113"/>
-      <c r="G339" s="78"/>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A340" s="88"/>
-      <c r="B340" s="118"/>
-      <c r="C340" s="115"/>
+      <c r="F339" s="81"/>
+      <c r="G339" s="72"/>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A340" s="83"/>
+      <c r="B340" s="89"/>
+      <c r="C340" s="86"/>
       <c r="D340" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="E340" s="30" t="s">
+      <c r="E340" s="25" t="s">
         <v>295</v>
       </c>
-      <c r="F340" s="113"/>
-      <c r="G340" s="78"/>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A341" s="88"/>
-      <c r="B341" s="118"/>
-      <c r="C341" s="115"/>
+      <c r="F340" s="81"/>
+      <c r="G340" s="72"/>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A341" s="83"/>
+      <c r="B341" s="89"/>
+      <c r="C341" s="86"/>
       <c r="D341" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="E341" s="30" t="s">
+      <c r="E341" s="25" t="s">
         <v>372</v>
       </c>
-      <c r="F341" s="113"/>
-      <c r="G341" s="78"/>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A342" s="89"/>
-      <c r="B342" s="119"/>
-      <c r="C342" s="116"/>
+      <c r="F341" s="81"/>
+      <c r="G341" s="72"/>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A342" s="84"/>
+      <c r="B342" s="90"/>
+      <c r="C342" s="87"/>
       <c r="D342" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="E342" s="30" t="s">
+      <c r="E342" s="25" t="s">
         <v>634</v>
       </c>
-      <c r="F342" s="113"/>
-      <c r="G342" s="78"/>
-    </row>
-    <row r="343" spans="1:7" ht="60" x14ac:dyDescent="0.25">
-      <c r="A343" s="54">
+      <c r="F342" s="81"/>
+      <c r="G342" s="72"/>
+    </row>
+    <row r="343" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A343" s="49">
         <v>125</v>
       </c>
-      <c r="B343" s="9" t="s">
+      <c r="B343" s="5" t="s">
         <v>123</v>
       </c>
       <c r="C343" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="D343" s="20"/>
-      <c r="E343" s="30"/>
-      <c r="F343" s="18" t="s">
+      <c r="E343" s="25"/>
+      <c r="F343" s="17" t="s">
         <v>783</v>
       </c>
-      <c r="G343" s="78"/>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A344" s="54">
+      <c r="G343" s="72"/>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A344" s="49">
         <v>126</v>
       </c>
-      <c r="B344" s="9" t="s">
+      <c r="B344" s="5" t="s">
         <v>124</v>
       </c>
       <c r="C344" s="4" t="s">
         <v>227</v>
       </c>
       <c r="D344" s="3"/>
-      <c r="E344" s="30"/>
+      <c r="E344" s="25"/>
       <c r="F344" s="6" t="s">
         <v>784</v>
       </c>
-      <c r="G344" s="78"/>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A345" s="54">
+      <c r="G344" s="72"/>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A345" s="49">
         <v>127</v>
       </c>
-      <c r="B345" s="9" t="s">
+      <c r="B345" s="5" t="s">
         <v>125</v>
       </c>
       <c r="C345" s="4" t="s">
         <v>228</v>
       </c>
       <c r="D345" s="3"/>
-      <c r="E345" s="30"/>
-      <c r="F345" s="18" t="s">
+      <c r="E345" s="25"/>
+      <c r="F345" s="17" t="s">
         <v>785</v>
       </c>
-      <c r="G345" s="78"/>
-    </row>
-    <row r="346" spans="1:7" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="79">
+      <c r="G345" s="72"/>
+    </row>
+    <row r="346" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A346" s="73">
         <v>128</v>
       </c>
-      <c r="B346" s="80" t="s">
+      <c r="B346" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C346" s="81" t="s">
+      <c r="C346" s="75" t="s">
         <v>226</v>
       </c>
-      <c r="D346" s="82"/>
-      <c r="E346" s="83"/>
-      <c r="F346" s="84" t="s">
+      <c r="D346" s="76"/>
+      <c r="E346" s="77"/>
+      <c r="F346" s="78" t="s">
         <v>786</v>
       </c>
-      <c r="G346" s="85"/>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B347" s="15"/>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B348" s="15"/>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B349" s="15"/>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B350" s="15"/>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B351" s="15"/>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B352" s="15"/>
-    </row>
-    <row r="353" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B353" s="15"/>
-    </row>
-    <row r="354" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B354" s="15"/>
-    </row>
-    <row r="355" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B355" s="15"/>
-    </row>
-    <row r="356" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B356" s="15"/>
-    </row>
-    <row r="357" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B357" s="15"/>
-    </row>
-    <row r="358" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B358" s="15"/>
-    </row>
-    <row r="359" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B359" s="15"/>
-    </row>
-    <row r="360" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B360" s="15"/>
-    </row>
-    <row r="361" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B361" s="15"/>
-    </row>
-    <row r="362" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B362" s="15"/>
+      <c r="G346" s="79"/>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B347" s="14"/>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B348" s="14"/>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B349" s="14"/>
+    </row>
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B350" s="14"/>
+    </row>
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B351" s="14"/>
+    </row>
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B352" s="14"/>
+    </row>
+    <row r="353" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B353" s="14"/>
+    </row>
+    <row r="354" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B354" s="14"/>
+    </row>
+    <row r="355" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B355" s="14"/>
+    </row>
+    <row r="356" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B356" s="14"/>
+    </row>
+    <row r="357" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B357" s="14"/>
+    </row>
+    <row r="358" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B358" s="14"/>
+    </row>
+    <row r="359" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B359" s="14"/>
+    </row>
+    <row r="360" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B360" s="14"/>
+    </row>
+    <row r="361" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B361" s="14"/>
+    </row>
+    <row r="362" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B362" s="14"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:F346"/>
+  <autoFilter ref="A2:F346" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="60">
-    <mergeCell ref="F325:F342"/>
-    <mergeCell ref="A195:A200"/>
-    <mergeCell ref="C325:C342"/>
-    <mergeCell ref="B325:B342"/>
-    <mergeCell ref="A325:A342"/>
-    <mergeCell ref="C228:C229"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="A228:A229"/>
-    <mergeCell ref="C255:C282"/>
-    <mergeCell ref="B255:B282"/>
-    <mergeCell ref="A255:A282"/>
+    <mergeCell ref="G255:G282"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F228:F229"/>
+    <mergeCell ref="C195:C201"/>
+    <mergeCell ref="B195:B201"/>
+    <mergeCell ref="G203:G211"/>
+    <mergeCell ref="C230:C243"/>
+    <mergeCell ref="B230:B243"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="B14:B121"/>
+    <mergeCell ref="C14:C121"/>
+    <mergeCell ref="A14:A121"/>
+    <mergeCell ref="D95:D100"/>
+    <mergeCell ref="D101:D104"/>
+    <mergeCell ref="D105:D114"/>
+    <mergeCell ref="D14:D23"/>
+    <mergeCell ref="D24:D34"/>
+    <mergeCell ref="D35:D43"/>
+    <mergeCell ref="D44:D53"/>
+    <mergeCell ref="A128:A138"/>
+    <mergeCell ref="B128:B138"/>
+    <mergeCell ref="D115:D118"/>
+    <mergeCell ref="D74:D87"/>
+    <mergeCell ref="D88:D94"/>
+    <mergeCell ref="D54:D63"/>
+    <mergeCell ref="D64:D73"/>
+    <mergeCell ref="C151:C153"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="A151:A153"/>
+    <mergeCell ref="C146:C150"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A146:A150"/>
     <mergeCell ref="C141:C142"/>
     <mergeCell ref="C123:C125"/>
     <mergeCell ref="B123:B125"/>
@@ -13278,39 +13272,18 @@
     <mergeCell ref="B175:B191"/>
     <mergeCell ref="A175:A191"/>
     <mergeCell ref="C128:C138"/>
-    <mergeCell ref="C151:C153"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="A151:A153"/>
-    <mergeCell ref="C146:C150"/>
-    <mergeCell ref="B146:B150"/>
-    <mergeCell ref="A146:A150"/>
-    <mergeCell ref="D14:D23"/>
-    <mergeCell ref="D24:D34"/>
-    <mergeCell ref="D35:D43"/>
-    <mergeCell ref="D44:D53"/>
-    <mergeCell ref="A128:A138"/>
-    <mergeCell ref="B128:B138"/>
-    <mergeCell ref="D115:D118"/>
-    <mergeCell ref="D74:D87"/>
-    <mergeCell ref="D88:D94"/>
-    <mergeCell ref="D54:D63"/>
-    <mergeCell ref="D64:D73"/>
+    <mergeCell ref="F325:F342"/>
+    <mergeCell ref="A195:A200"/>
+    <mergeCell ref="C325:C342"/>
+    <mergeCell ref="B325:B342"/>
+    <mergeCell ref="A325:A342"/>
+    <mergeCell ref="C228:C229"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="A228:A229"/>
+    <mergeCell ref="C255:C282"/>
+    <mergeCell ref="B255:B282"/>
+    <mergeCell ref="A255:A282"/>
     <mergeCell ref="A230:A243"/>
-    <mergeCell ref="G255:G282"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F228:F229"/>
-    <mergeCell ref="C195:C201"/>
-    <mergeCell ref="B195:B201"/>
-    <mergeCell ref="G203:G211"/>
-    <mergeCell ref="C230:C243"/>
-    <mergeCell ref="B230:B243"/>
-    <mergeCell ref="D119:D121"/>
-    <mergeCell ref="B14:B121"/>
-    <mergeCell ref="C14:C121"/>
-    <mergeCell ref="A14:A121"/>
-    <mergeCell ref="D95:D100"/>
-    <mergeCell ref="D101:D104"/>
-    <mergeCell ref="D105:D114"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.39370078740157483" bottom="0" header="0" footer="0"/>
